--- a/TestDIR/Project_Pandas_2026_10_04_market/Raw/table_silver/silverCompras_ETL.xlsx
+++ b/TestDIR/Project_Pandas_2026_10_04_market/Raw/table_silver/silverCompras_ETL.xlsx
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>163</v>
+        <v>163.39</v>
       </c>
       <c r="J2" s="1" t="n">
         <v>46023</v>
@@ -553,7 +553,7 @@
         <v>1001</v>
       </c>
       <c r="O2" t="n">
-        <v>2.963636363636364</v>
+        <v>2.970727272727272</v>
       </c>
     </row>
     <row r="3">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>335</v>
+        <v>335.78</v>
       </c>
       <c r="J3" s="1" t="n">
         <v>46023</v>
@@ -612,7 +612,7 @@
         <v>1001</v>
       </c>
       <c r="O3" t="n">
-        <v>2.815126050420168</v>
+        <v>2.821680672268907</v>
       </c>
     </row>
     <row r="4">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>243</v>
+        <v>243.92</v>
       </c>
       <c r="J4" s="1" t="n">
         <v>46023</v>
@@ -671,7 +671,7 @@
         <v>1001</v>
       </c>
       <c r="O4" t="n">
-        <v>2.113043478260869</v>
+        <v>2.121043478260869</v>
       </c>
     </row>
     <row r="5">
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>123</v>
+        <v>123.78</v>
       </c>
       <c r="J5" s="1" t="n">
         <v>46023</v>
@@ -730,7 +730,7 @@
         <v>1001</v>
       </c>
       <c r="O5" t="n">
-        <v>3</v>
+        <v>3.019024390243902</v>
       </c>
     </row>
     <row r="6">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>235</v>
+        <v>235.48</v>
       </c>
       <c r="J6" s="1" t="n">
         <v>46023</v>
@@ -789,7 +789,7 @@
         <v>1001</v>
       </c>
       <c r="O6" t="n">
-        <v>2.764705882352941</v>
+        <v>2.77035294117647</v>
       </c>
     </row>
     <row r="7">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1514</v>
+        <v>1514.03</v>
       </c>
       <c r="J7" s="1" t="n">
         <v>46024</v>
@@ -848,7 +848,7 @@
         <v>1002</v>
       </c>
       <c r="O7" t="n">
-        <v>27.52727272727273</v>
+        <v>27.52781818181818</v>
       </c>
     </row>
     <row r="8">
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1063</v>
+        <v>1063.28</v>
       </c>
       <c r="J8" s="1" t="n">
         <v>46024</v>
@@ -907,7 +907,7 @@
         <v>1002</v>
       </c>
       <c r="O8" t="n">
-        <v>36.6551724137931</v>
+        <v>36.6648275862069</v>
       </c>
     </row>
     <row r="9">
@@ -948,7 +948,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>753</v>
+        <v>753.7</v>
       </c>
       <c r="J9" s="1" t="n">
         <v>46024</v>
@@ -966,7 +966,7 @@
         <v>1002</v>
       </c>
       <c r="O9" t="n">
-        <v>35.85714285714285</v>
+        <v>35.89047619047619</v>
       </c>
     </row>
     <row r="10">
@@ -1007,7 +1007,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1195</v>
+        <v>1195.59</v>
       </c>
       <c r="J10" s="1" t="n">
         <v>46024</v>
@@ -1025,7 +1025,7 @@
         <v>1002</v>
       </c>
       <c r="O10" t="n">
-        <v>24.38775510204082</v>
+        <v>24.39979591836735</v>
       </c>
     </row>
     <row r="11">
@@ -1066,7 +1066,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>178</v>
+        <v>178.21</v>
       </c>
       <c r="J11" s="1" t="n">
         <v>46025</v>
@@ -1084,7 +1084,7 @@
         <v>1001</v>
       </c>
       <c r="O11" t="n">
-        <v>3.296296296296296</v>
+        <v>3.300185185185185</v>
       </c>
     </row>
     <row r="12">
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>253</v>
+        <v>253.56</v>
       </c>
       <c r="J12" s="1" t="n">
         <v>46025</v>
@@ -1143,7 +1143,7 @@
         <v>1001</v>
       </c>
       <c r="O12" t="n">
-        <v>3.465753424657534</v>
+        <v>3.473424657534247</v>
       </c>
     </row>
     <row r="13">
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>234</v>
+        <v>234.29</v>
       </c>
       <c r="J13" s="1" t="n">
         <v>46025</v>
@@ -1198,7 +1198,7 @@
         <v>1001</v>
       </c>
       <c r="O13" t="n">
-        <v>2.070796460176991</v>
+        <v>2.073362831858407</v>
       </c>
     </row>
     <row r="14">
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>117</v>
+        <v>117.32</v>
       </c>
       <c r="J14" s="1" t="n">
         <v>46025</v>
@@ -1257,7 +1257,7 @@
         <v>1001</v>
       </c>
       <c r="O14" t="n">
-        <v>2.207547169811321</v>
+        <v>2.213584905660377</v>
       </c>
     </row>
     <row r="15">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>R$ 368.61</t>
+          <t>R$ 368,61</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1298,7 +1298,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>368.61</v>
       </c>
       <c r="J15" s="1" t="n">
         <v>46025</v>
@@ -1316,7 +1316,7 @@
         <v>1001</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.07175</v>
       </c>
     </row>
     <row r="16">
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>240</v>
+        <v>240.75</v>
       </c>
       <c r="J16" s="1" t="n">
         <v>46027</v>
@@ -1375,7 +1375,7 @@
         <v>1001</v>
       </c>
       <c r="O16" t="n">
-        <v>3.037974683544304</v>
+        <v>3.04746835443038</v>
       </c>
     </row>
     <row r="17">
@@ -1416,7 +1416,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>164</v>
+        <v>164.63</v>
       </c>
       <c r="J17" s="1" t="n">
         <v>46027</v>
@@ -1434,7 +1434,7 @@
         <v>1001</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.216216216216216</v>
+        <v>-2.224729729729729</v>
       </c>
     </row>
     <row r="18">
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>309</v>
+        <v>309.98</v>
       </c>
       <c r="J18" s="1" t="n">
         <v>46027</v>
@@ -1493,7 +1493,7 @@
         <v>1001</v>
       </c>
       <c r="O18" t="n">
-        <v>3.029411764705882</v>
+        <v>3.039019607843137</v>
       </c>
     </row>
     <row r="19">
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>308</v>
+        <v>308.47</v>
       </c>
       <c r="J19" s="1" t="n">
         <v>46027</v>
@@ -1552,7 +1552,7 @@
         <v>1001</v>
       </c>
       <c r="O19" t="n">
-        <v>3.242105263157895</v>
+        <v>3.247052631578948</v>
       </c>
     </row>
     <row r="20">
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>266</v>
+        <v>266.18</v>
       </c>
       <c r="J20" s="1" t="n">
         <v>46027</v>
@@ -1611,7 +1611,7 @@
         <v>1001</v>
       </c>
       <c r="O20" t="n">
-        <v>2.770833333333333</v>
+        <v>2.772708333333334</v>
       </c>
     </row>
     <row r="21">
@@ -1652,7 +1652,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1680</v>
+        <v>1680.06</v>
       </c>
       <c r="J21" s="1" t="n">
         <v>46027</v>
@@ -1670,7 +1670,7 @@
         <v>1002</v>
       </c>
       <c r="O21" t="n">
-        <v>35.74468085106383</v>
+        <v>35.74595744680851</v>
       </c>
     </row>
     <row r="22">
@@ -1711,7 +1711,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1383</v>
+        <v>1383.36</v>
       </c>
       <c r="J22" s="1" t="n">
         <v>46027</v>
@@ -1729,7 +1729,7 @@
         <v>1002</v>
       </c>
       <c r="O22" t="n">
-        <v>37.37837837837838</v>
+        <v>37.38810810810811</v>
       </c>
     </row>
     <row r="23">
@@ -1770,7 +1770,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1061</v>
+        <v>1061.88</v>
       </c>
       <c r="J23" s="1" t="n">
         <v>46027</v>
@@ -1788,7 +1788,7 @@
         <v>1002</v>
       </c>
       <c r="O23" t="n">
-        <v>33.15625</v>
+        <v>33.18375</v>
       </c>
     </row>
     <row r="24">
@@ -1829,7 +1829,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1811</v>
+        <v>1811.76</v>
       </c>
       <c r="J24" s="1" t="n">
         <v>46027</v>
@@ -1847,7 +1847,7 @@
         <v>1002</v>
       </c>
       <c r="O24" t="n">
-        <v>37.72916666666666</v>
+        <v>37.745</v>
       </c>
     </row>
     <row r="25">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>R$ 206.09</t>
+          <t>R$ 206,09</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1888,7 +1888,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>206.09</v>
       </c>
       <c r="J25" s="1" t="n">
         <v>46029</v>
@@ -1906,7 +1906,7 @@
         <v>1001</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>2.124639175257732</v>
       </c>
     </row>
     <row r="26">
@@ -1943,7 +1943,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>335</v>
+        <v>335.54</v>
       </c>
       <c r="J26" s="1" t="n">
         <v>46029</v>
@@ -1961,7 +1961,7 @@
         <v>1001</v>
       </c>
       <c r="O26" t="n">
-        <v>-2.815126050420168</v>
+        <v>-2.819663865546219</v>
       </c>
     </row>
     <row r="27">
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>244</v>
+        <v>244.34</v>
       </c>
       <c r="J27" s="1" t="n">
         <v>46029</v>
@@ -2020,7 +2020,7 @@
         <v>1001</v>
       </c>
       <c r="O27" t="n">
-        <v>2.870588235294118</v>
+        <v>2.874588235294118</v>
       </c>
     </row>
     <row r="28">
@@ -2061,7 +2061,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>125</v>
+        <v>125.22</v>
       </c>
       <c r="J28" s="1" t="n">
         <v>46029</v>
@@ -2079,7 +2079,7 @@
         <v>1001</v>
       </c>
       <c r="O28" t="n">
-        <v>2.192982456140351</v>
+        <v>2.196842105263158</v>
       </c>
     </row>
     <row r="29">
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1041</v>
+        <v>1041.61</v>
       </c>
       <c r="J30" s="1" t="n">
         <v>46029</v>
@@ -2197,7 +2197,7 @@
         <v>1002</v>
       </c>
       <c r="O30" t="n">
-        <v>26.69230769230769</v>
+        <v>26.70794871794871</v>
       </c>
     </row>
     <row r="31">
@@ -2238,7 +2238,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1843</v>
+        <v>1843.69</v>
       </c>
       <c r="J31" s="1" t="n">
         <v>46029</v>
@@ -2256,7 +2256,7 @@
         <v>1002</v>
       </c>
       <c r="O31" t="n">
-        <v>34.77358490566038</v>
+        <v>34.78660377358491</v>
       </c>
     </row>
     <row r="32">
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>611</v>
+        <v>611.3200000000001</v>
       </c>
       <c r="J32" s="1" t="n">
         <v>46029</v>
@@ -2315,7 +2315,7 @@
         <v>1002</v>
       </c>
       <c r="O32" t="n">
-        <v>23.5</v>
+        <v>23.51230769230769</v>
       </c>
     </row>
     <row r="33">
@@ -2356,7 +2356,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1278</v>
+        <v>1278.87</v>
       </c>
       <c r="J33" s="1" t="n">
         <v>46029</v>
@@ -2374,7 +2374,7 @@
         <v>1002</v>
       </c>
       <c r="O33" t="n">
-        <v>30.42857142857143</v>
+        <v>30.44928571428571</v>
       </c>
     </row>
     <row r="34">
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>280</v>
+        <v>280.9</v>
       </c>
       <c r="J34" s="1" t="n">
         <v>46031</v>
@@ -2433,7 +2433,7 @@
         <v>1001</v>
       </c>
       <c r="O34" t="n">
-        <v>2.666666666666667</v>
+        <v>2.675238095238095</v>
       </c>
     </row>
     <row r="35">
@@ -2474,7 +2474,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>326</v>
+        <v>326.22</v>
       </c>
       <c r="J35" s="1" t="n">
         <v>46031</v>
@@ -2492,7 +2492,7 @@
         <v>1001</v>
       </c>
       <c r="O35" t="n">
-        <v>2.884955752212389</v>
+        <v>2.886902654867257</v>
       </c>
     </row>
     <row r="36">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>R$ 206.22</t>
+          <t>R$ 206,22</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -2529,7 +2529,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>206.22</v>
       </c>
       <c r="J36" s="1" t="n">
         <v>46031</v>
@@ -2547,7 +2547,7 @@
         <v>1001</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>2.104285714285714</v>
       </c>
     </row>
     <row r="37">
@@ -2584,7 +2584,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>174</v>
+        <v>174.66</v>
       </c>
       <c r="J37" s="1" t="n">
         <v>46031</v>
@@ -2602,7 +2602,7 @@
         <v>1001</v>
       </c>
       <c r="O37" t="n">
-        <v>-2.806451612903226</v>
+        <v>-2.817096774193548</v>
       </c>
     </row>
     <row r="38">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>129</v>
+        <v>129.97</v>
       </c>
       <c r="J38" s="1" t="n">
         <v>46031</v>
@@ -2661,7 +2661,7 @@
         <v>1001</v>
       </c>
       <c r="O38" t="n">
-        <v>2.015625</v>
+        <v>2.03078125</v>
       </c>
     </row>
     <row r="39">
@@ -2702,7 +2702,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>485</v>
+        <v>485.26</v>
       </c>
       <c r="J39" s="1" t="n">
         <v>46031</v>
@@ -2720,7 +2720,7 @@
         <v>1002</v>
       </c>
       <c r="O39" t="n">
-        <v>17.32142857142857</v>
+        <v>17.33071428571429</v>
       </c>
     </row>
     <row r="40">
@@ -2761,7 +2761,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>905</v>
+        <v>905.9299999999999</v>
       </c>
       <c r="J40" s="1" t="n">
         <v>46031</v>
@@ -2779,7 +2779,7 @@
         <v>1002</v>
       </c>
       <c r="O40" t="n">
-        <v>24.45945945945946</v>
+        <v>24.48459459459459</v>
       </c>
     </row>
     <row r="41">
@@ -2820,7 +2820,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>934</v>
+        <v>934.23</v>
       </c>
       <c r="J41" s="1" t="n">
         <v>46031</v>
@@ -2838,7 +2838,7 @@
         <v>1002</v>
       </c>
       <c r="O41" t="n">
-        <v>21.22727272727273</v>
+        <v>21.2325</v>
       </c>
     </row>
     <row r="42">
@@ -2879,7 +2879,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>918</v>
+        <v>918.9299999999999</v>
       </c>
       <c r="J42" s="1" t="n">
         <v>46031</v>
@@ -2897,7 +2897,7 @@
         <v>1002</v>
       </c>
       <c r="O42" t="n">
-        <v>25.5</v>
+        <v>25.52583333333333</v>
       </c>
     </row>
     <row r="43">
@@ -2938,7 +2938,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>264</v>
+        <v>264.02</v>
       </c>
       <c r="J43" s="1" t="n">
         <v>46033</v>
@@ -2956,7 +2956,7 @@
         <v>1001</v>
       </c>
       <c r="O43" t="n">
-        <v>2.666666666666667</v>
+        <v>2.666868686868687</v>
       </c>
     </row>
     <row r="44">
@@ -2997,7 +2997,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>178</v>
+        <v>178.39</v>
       </c>
       <c r="J44" s="1" t="n">
         <v>46033</v>
@@ -3015,7 +3015,7 @@
         <v>1001</v>
       </c>
       <c r="O44" t="n">
-        <v>3.423076923076923</v>
+        <v>3.430576923076923</v>
       </c>
     </row>
     <row r="45">
@@ -3056,7 +3056,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>327</v>
+        <v>327.61</v>
       </c>
       <c r="J45" s="1" t="n">
         <v>46033</v>
@@ -3074,7 +3074,7 @@
         <v>1001</v>
       </c>
       <c r="O45" t="n">
-        <v>3</v>
+        <v>3.00559633027523</v>
       </c>
     </row>
     <row r="46">
@@ -3115,7 +3115,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>238</v>
+        <v>238.64</v>
       </c>
       <c r="J46" s="1" t="n">
         <v>46033</v>
@@ -3133,7 +3133,7 @@
         <v>1001</v>
       </c>
       <c r="O46" t="n">
-        <v>2.8</v>
+        <v>2.807529411764706</v>
       </c>
     </row>
     <row r="47">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>R$ 316.88</t>
+          <t>R$ 316,88</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3174,7 +3174,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>316.88</v>
       </c>
       <c r="J47" s="1" t="n">
         <v>46033</v>
@@ -3192,7 +3192,7 @@
         <v>1001</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>2.854774774774775</v>
       </c>
     </row>
     <row r="48">
@@ -3233,7 +3233,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>440</v>
+        <v>440.7</v>
       </c>
       <c r="J48" s="1" t="n">
         <v>46034</v>
@@ -3251,7 +3251,7 @@
         <v>1002</v>
       </c>
       <c r="O48" t="n">
-        <v>15.71428571428571</v>
+        <v>15.73928571428571</v>
       </c>
     </row>
     <row r="49">
@@ -3292,7 +3292,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>828</v>
+        <v>828.35</v>
       </c>
       <c r="J49" s="1" t="n">
         <v>46034</v>
@@ -3310,7 +3310,7 @@
         <v>1002</v>
       </c>
       <c r="O49" t="n">
-        <v>17.61702127659574</v>
+        <v>17.62446808510638</v>
       </c>
     </row>
     <row r="50">
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>943</v>
+        <v>943.66</v>
       </c>
       <c r="J50" s="1" t="n">
         <v>46034</v>
@@ -3369,7 +3369,7 @@
         <v>1002</v>
       </c>
       <c r="O50" t="n">
-        <v>30.41935483870968</v>
+        <v>30.44064516129032</v>
       </c>
     </row>
     <row r="51">
@@ -3410,7 +3410,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1068</v>
+        <v>1068.52</v>
       </c>
       <c r="J51" s="1" t="n">
         <v>46034</v>
@@ -3428,7 +3428,7 @@
         <v>1002</v>
       </c>
       <c r="O51" t="n">
-        <v>28.86486486486486</v>
+        <v>28.87891891891892</v>
       </c>
     </row>
     <row r="52">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>R$ 161.66</t>
+          <t>R$ 161,66</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3469,7 +3469,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>161.66</v>
       </c>
       <c r="J52" s="1" t="n">
         <v>46035</v>
@@ -3487,7 +3487,7 @@
         <v>1001</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>2.02075</v>
       </c>
     </row>
     <row r="53">
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>102</v>
+        <v>102.67</v>
       </c>
       <c r="J53" s="1" t="n">
         <v>46035</v>
@@ -3546,7 +3546,7 @@
         <v>1001</v>
       </c>
       <c r="O53" t="n">
-        <v>2.170212765957447</v>
+        <v>2.184468085106383</v>
       </c>
     </row>
     <row r="54">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>R$ 238.57</t>
+          <t>R$ 238,57</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3587,7 +3587,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>238.57</v>
       </c>
       <c r="J54" s="1" t="n">
         <v>46035</v>
@@ -3605,7 +3605,7 @@
         <v>1001</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>2.982125</v>
       </c>
     </row>
     <row r="55">
@@ -3642,7 +3642,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>211</v>
+        <v>211.13</v>
       </c>
       <c r="J55" s="1" t="n">
         <v>46035</v>
@@ -3660,7 +3660,7 @@
         <v>1001</v>
       </c>
       <c r="O55" t="n">
-        <v>2.6375</v>
+        <v>2.639125</v>
       </c>
     </row>
     <row r="56">
@@ -3687,7 +3687,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>R$ 294.55</t>
+          <t>R$ 294,55</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3701,7 +3701,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>294.55</v>
       </c>
       <c r="J56" s="1" t="n">
         <v>46035</v>
@@ -3719,7 +3719,7 @@
         <v>1001</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>3.385632183908046</v>
       </c>
     </row>
     <row r="57">
@@ -3760,7 +3760,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>755</v>
+        <v>755.6799999999999</v>
       </c>
       <c r="J57" s="1" t="n">
         <v>46036</v>
@@ -3778,7 +3778,7 @@
         <v>1002</v>
       </c>
       <c r="O57" t="n">
-        <v>32.82608695652174</v>
+        <v>32.85565217391304</v>
       </c>
     </row>
     <row r="58">
@@ -3819,7 +3819,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1207</v>
+        <v>1207.38</v>
       </c>
       <c r="J58" s="1" t="n">
         <v>46036</v>
@@ -3837,7 +3837,7 @@
         <v>1002</v>
       </c>
       <c r="O58" t="n">
-        <v>31.76315789473684</v>
+        <v>31.77315789473684</v>
       </c>
     </row>
     <row r="59">
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1315</v>
+        <v>1315.59</v>
       </c>
       <c r="J59" s="1" t="n">
         <v>46036</v>
@@ -3896,7 +3896,7 @@
         <v>1002</v>
       </c>
       <c r="O59" t="n">
-        <v>33.71794871794872</v>
+        <v>33.73307692307692</v>
       </c>
     </row>
     <row r="60">
@@ -3992,7 +3992,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>111</v>
+        <v>111.02</v>
       </c>
       <c r="J61" s="1" t="n">
         <v>46037</v>
@@ -4010,7 +4010,7 @@
         <v>1001</v>
       </c>
       <c r="O61" t="n">
-        <v>2.055555555555555</v>
+        <v>2.055925925925926</v>
       </c>
     </row>
     <row r="62">
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>223</v>
+        <v>223.64</v>
       </c>
       <c r="J62" s="1" t="n">
         <v>46037</v>
@@ -4069,7 +4069,7 @@
         <v>1001</v>
       </c>
       <c r="O62" t="n">
-        <v>-2.858974358974359</v>
+        <v>-2.867179487179487</v>
       </c>
     </row>
     <row r="63">
@@ -4106,7 +4106,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>221</v>
+        <v>221.37</v>
       </c>
       <c r="J63" s="1" t="n">
         <v>46037</v>
@@ -4124,7 +4124,7 @@
         <v>1001</v>
       </c>
       <c r="O63" t="n">
-        <v>3.157142857142857</v>
+        <v>3.162428571428571</v>
       </c>
     </row>
     <row r="64">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>R$ 259.69</t>
+          <t>R$ 259,69</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4165,7 +4165,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>259.69</v>
       </c>
       <c r="J64" s="1" t="n">
         <v>46037</v>
@@ -4183,7 +4183,7 @@
         <v>1001</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>2.382477064220184</v>
       </c>
     </row>
     <row r="65">
@@ -4224,7 +4224,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>257</v>
+        <v>257.83</v>
       </c>
       <c r="J65" s="1" t="n">
         <v>46037</v>
@@ -4242,7 +4242,7 @@
         <v>1001</v>
       </c>
       <c r="O65" t="n">
-        <v>3.426666666666667</v>
+        <v>3.437733333333333</v>
       </c>
     </row>
     <row r="66">
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>891</v>
+        <v>891.7</v>
       </c>
       <c r="J66" s="1" t="n">
         <v>46038</v>
@@ -4301,7 +4301,7 @@
         <v>1002</v>
       </c>
       <c r="O66" t="n">
-        <v>35.64</v>
+        <v>35.668</v>
       </c>
     </row>
     <row r="67">
@@ -4342,7 +4342,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1827</v>
+        <v>1827.09</v>
       </c>
       <c r="J67" s="1" t="n">
         <v>46038</v>
@@ -4360,7 +4360,7 @@
         <v>1002</v>
       </c>
       <c r="O67" t="n">
-        <v>35.13461538461539</v>
+        <v>35.13634615384616</v>
       </c>
     </row>
     <row r="68">
@@ -4401,7 +4401,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>707</v>
+        <v>707.54</v>
       </c>
       <c r="J68" s="1" t="n">
         <v>46038</v>
@@ -4419,7 +4419,7 @@
         <v>1002</v>
       </c>
       <c r="O68" t="n">
-        <v>30.73913043478261</v>
+        <v>30.76260869565217</v>
       </c>
     </row>
     <row r="69">
@@ -4460,7 +4460,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>728</v>
+        <v>728.7</v>
       </c>
       <c r="J69" s="1" t="n">
         <v>46038</v>
@@ -4478,7 +4478,7 @@
         <v>1002</v>
       </c>
       <c r="O69" t="n">
-        <v>14.56</v>
+        <v>14.574</v>
       </c>
     </row>
     <row r="70">
@@ -4519,7 +4519,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>289</v>
+        <v>289.86</v>
       </c>
       <c r="J70" s="1" t="n">
         <v>46039</v>
@@ -4537,7 +4537,7 @@
         <v>1001</v>
       </c>
       <c r="O70" t="n">
-        <v>3.175824175824176</v>
+        <v>3.185274725274725</v>
       </c>
     </row>
     <row r="71">
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>174</v>
+        <v>174.61</v>
       </c>
       <c r="J71" s="1" t="n">
         <v>46039</v>
@@ -4592,7 +4592,7 @@
         <v>1001</v>
       </c>
       <c r="O71" t="n">
-        <v>2.676923076923077</v>
+        <v>2.686307692307693</v>
       </c>
     </row>
     <row r="72">
@@ -4633,7 +4633,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>298</v>
+        <v>298.2</v>
       </c>
       <c r="J72" s="1" t="n">
         <v>46039</v>
@@ -4651,7 +4651,7 @@
         <v>1001</v>
       </c>
       <c r="O72" t="n">
-        <v>2.614035087719298</v>
+        <v>2.61578947368421</v>
       </c>
     </row>
     <row r="73">
@@ -4678,7 +4678,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>R$ 313.62</t>
+          <t>R$ 313,62</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4692,7 +4692,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0</v>
+        <v>313.62</v>
       </c>
       <c r="J73" s="1" t="n">
         <v>46039</v>
@@ -4710,7 +4710,7 @@
         <v>1001</v>
       </c>
       <c r="O73" t="n">
-        <v>0</v>
+        <v>2.958679245283019</v>
       </c>
     </row>
     <row r="74">
@@ -4747,7 +4747,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>255</v>
+        <v>255.37</v>
       </c>
       <c r="J74" s="1" t="n">
         <v>46039</v>
@@ -4765,7 +4765,7 @@
         <v>1001</v>
       </c>
       <c r="O74" t="n">
-        <v>3.493150684931507</v>
+        <v>3.498219178082192</v>
       </c>
     </row>
     <row r="75">
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>295</v>
+        <v>295.25</v>
       </c>
       <c r="J75" s="1" t="n">
         <v>46041</v>
@@ -4824,7 +4824,7 @@
         <v>1001</v>
       </c>
       <c r="O75" t="n">
-        <v>2.587719298245614</v>
+        <v>2.589912280701754</v>
       </c>
     </row>
     <row r="76">
@@ -4865,7 +4865,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>132</v>
+        <v>132.77</v>
       </c>
       <c r="J76" s="1" t="n">
         <v>46041</v>
@@ -4883,7 +4883,7 @@
         <v>1001</v>
       </c>
       <c r="O76" t="n">
-        <v>2.2</v>
+        <v>2.212833333333334</v>
       </c>
     </row>
     <row r="77">
@@ -4910,7 +4910,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>R$ 228.24</t>
+          <t>R$ 228,24</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -4924,7 +4924,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0</v>
+        <v>228.24</v>
       </c>
       <c r="J77" s="1" t="n">
         <v>46041</v>
@@ -4942,7 +4942,7 @@
         <v>1001</v>
       </c>
       <c r="O77" t="n">
-        <v>-0</v>
+        <v>-2.889113924050633</v>
       </c>
     </row>
     <row r="78">
@@ -4979,7 +4979,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>266</v>
+        <v>266.35</v>
       </c>
       <c r="J78" s="1" t="n">
         <v>46041</v>
@@ -4997,7 +4997,7 @@
         <v>1001</v>
       </c>
       <c r="O78" t="n">
-        <v>3.454545454545455</v>
+        <v>3.459090909090909</v>
       </c>
     </row>
     <row r="79">
@@ -5038,7 +5038,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>139</v>
+        <v>139.76</v>
       </c>
       <c r="J79" s="1" t="n">
         <v>46041</v>
@@ -5056,7 +5056,7 @@
         <v>1001</v>
       </c>
       <c r="O79" t="n">
-        <v>3.390243902439024</v>
+        <v>3.408780487804878</v>
       </c>
     </row>
     <row r="80">
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>974</v>
+        <v>974.8</v>
       </c>
       <c r="J80" s="1" t="n">
         <v>46041</v>
@@ -5115,7 +5115,7 @@
         <v>1002</v>
       </c>
       <c r="O80" t="n">
-        <v>32.46666666666667</v>
+        <v>32.49333333333333</v>
       </c>
     </row>
     <row r="81">
@@ -5156,7 +5156,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1102</v>
+        <v>1102.22</v>
       </c>
       <c r="J81" s="1" t="n">
         <v>46041</v>
@@ -5174,7 +5174,7 @@
         <v>1002</v>
       </c>
       <c r="O81" t="n">
-        <v>27.55</v>
+        <v>27.5555</v>
       </c>
     </row>
     <row r="82">
@@ -5215,7 +5215,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>726</v>
+        <v>726.4299999999999</v>
       </c>
       <c r="J82" s="1" t="n">
         <v>46041</v>
@@ -5233,7 +5233,7 @@
         <v>1002</v>
       </c>
       <c r="O82" t="n">
-        <v>26.88888888888889</v>
+        <v>26.90481481481481</v>
       </c>
     </row>
     <row r="83">
@@ -5274,7 +5274,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>632</v>
+        <v>632.84</v>
       </c>
       <c r="J83" s="1" t="n">
         <v>46041</v>
@@ -5292,7 +5292,7 @@
         <v>1002</v>
       </c>
       <c r="O83" t="n">
-        <v>14.69767441860465</v>
+        <v>14.71720930232558</v>
       </c>
     </row>
     <row r="84">
@@ -5329,7 +5329,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>236</v>
+        <v>236.5</v>
       </c>
       <c r="J84" s="1" t="n">
         <v>46043</v>
@@ -5347,7 +5347,7 @@
         <v>1001</v>
       </c>
       <c r="O84" t="n">
-        <v>2.185185185185185</v>
+        <v>2.189814814814815</v>
       </c>
     </row>
     <row r="85">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>145</v>
+        <v>145.59</v>
       </c>
       <c r="J85" s="1" t="n">
         <v>46043</v>
@@ -5406,7 +5406,7 @@
         <v>1001</v>
       </c>
       <c r="O85" t="n">
-        <v>2.959183673469388</v>
+        <v>2.971224489795918</v>
       </c>
     </row>
     <row r="86">
@@ -5447,7 +5447,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>139</v>
+        <v>139.59</v>
       </c>
       <c r="J86" s="1" t="n">
         <v>46043</v>
@@ -5465,7 +5465,7 @@
         <v>1001</v>
       </c>
       <c r="O86" t="n">
-        <v>2.527272727272727</v>
+        <v>2.538</v>
       </c>
     </row>
     <row r="87">
@@ -5502,7 +5502,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>160</v>
+        <v>160.63</v>
       </c>
       <c r="J87" s="1" t="n">
         <v>46043</v>
@@ -5520,7 +5520,7 @@
         <v>1001</v>
       </c>
       <c r="O87" t="n">
-        <v>3.2</v>
+        <v>3.2126</v>
       </c>
     </row>
     <row r="88">
@@ -5557,7 +5557,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>193</v>
+        <v>193.28</v>
       </c>
       <c r="J88" s="1" t="n">
         <v>46043</v>
@@ -5575,7 +5575,7 @@
         <v>1001</v>
       </c>
       <c r="O88" t="n">
-        <v>2.838235294117647</v>
+        <v>2.842352941176471</v>
       </c>
     </row>
     <row r="89">
@@ -5616,7 +5616,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1218</v>
+        <v>1218.03</v>
       </c>
       <c r="J89" s="1" t="n">
         <v>46043</v>
@@ -5634,7 +5634,7 @@
         <v>1002</v>
       </c>
       <c r="O89" t="n">
-        <v>23.88235294117647</v>
+        <v>23.88294117647059</v>
       </c>
     </row>
     <row r="90">
@@ -5675,7 +5675,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>928</v>
+        <v>928.29</v>
       </c>
       <c r="J90" s="1" t="n">
         <v>46043</v>
@@ -5693,7 +5693,7 @@
         <v>1002</v>
       </c>
       <c r="O90" t="n">
-        <v>18.93877551020408</v>
+        <v>18.94469387755102</v>
       </c>
     </row>
     <row r="91">
@@ -5734,7 +5734,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1630</v>
+        <v>1630.87</v>
       </c>
       <c r="J91" s="1" t="n">
         <v>46043</v>
@@ -5752,7 +5752,7 @@
         <v>1002</v>
       </c>
       <c r="O91" t="n">
-        <v>35.43478260869565</v>
+        <v>35.45369565217391</v>
       </c>
     </row>
     <row r="92">
@@ -5793,7 +5793,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>566</v>
+        <v>566.55</v>
       </c>
       <c r="J92" s="1" t="n">
         <v>46043</v>
@@ -5811,7 +5811,7 @@
         <v>1002</v>
       </c>
       <c r="O92" t="n">
-        <v>17.15151515151515</v>
+        <v>17.16818181818182</v>
       </c>
     </row>
     <row r="93">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>R$ 235.6</t>
+          <t>R$ 235,6</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -5852,7 +5852,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0</v>
+        <v>235.6</v>
       </c>
       <c r="J93" s="1" t="n">
         <v>46045</v>
@@ -5870,7 +5870,7 @@
         <v>1001</v>
       </c>
       <c r="O93" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="94">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>R$ 265.82</t>
+          <t>R$ 265,82</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0</v>
+        <v>265.82</v>
       </c>
       <c r="J94" s="1" t="n">
         <v>46045</v>
@@ -5929,7 +5929,7 @@
         <v>1001</v>
       </c>
       <c r="O94" t="n">
-        <v>0</v>
+        <v>2.215166666666667</v>
       </c>
     </row>
     <row r="95">
@@ -5970,7 +5970,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>229</v>
+        <v>229.68</v>
       </c>
       <c r="J95" s="1" t="n">
         <v>46045</v>
@@ -5988,7 +5988,7 @@
         <v>1001</v>
       </c>
       <c r="O95" t="n">
-        <v>2.026548672566372</v>
+        <v>2.032566371681416</v>
       </c>
     </row>
     <row r="96">
@@ -6025,7 +6025,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>227</v>
+        <v>227.59</v>
       </c>
       <c r="J96" s="1" t="n">
         <v>46045</v>
@@ -6043,7 +6043,7 @@
         <v>1001</v>
       </c>
       <c r="O96" t="n">
-        <v>2.734939759036144</v>
+        <v>2.742048192771084</v>
       </c>
     </row>
     <row r="97">
@@ -6080,7 +6080,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>323</v>
+        <v>323.98</v>
       </c>
       <c r="J97" s="1" t="n">
         <v>46045</v>
@@ -6098,7 +6098,7 @@
         <v>1001</v>
       </c>
       <c r="O97" t="n">
-        <v>2.963302752293578</v>
+        <v>2.972293577981652</v>
       </c>
     </row>
     <row r="98">
@@ -6139,7 +6139,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>411</v>
+        <v>411.8</v>
       </c>
       <c r="J98" s="1" t="n">
         <v>46045</v>
@@ -6157,7 +6157,7 @@
         <v>1002</v>
       </c>
       <c r="O98" t="n">
-        <v>13.25806451612903</v>
+        <v>13.28387096774194</v>
       </c>
     </row>
     <row r="99">
@@ -6198,7 +6198,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>616</v>
+        <v>616.51</v>
       </c>
       <c r="J99" s="1" t="n">
         <v>46045</v>
@@ -6216,7 +6216,7 @@
         <v>1002</v>
       </c>
       <c r="O99" t="n">
-        <v>22</v>
+        <v>22.01821428571429</v>
       </c>
     </row>
     <row r="100">
@@ -6257,7 +6257,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1799</v>
+        <v>1799.3</v>
       </c>
       <c r="J100" s="1" t="n">
         <v>46045</v>
@@ -6275,7 +6275,7 @@
         <v>1002</v>
       </c>
       <c r="O100" t="n">
-        <v>35.98</v>
+        <v>35.986</v>
       </c>
     </row>
     <row r="101">
@@ -6316,7 +6316,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>280</v>
+        <v>280.25</v>
       </c>
       <c r="J101" s="1" t="n">
         <v>46045</v>
@@ -6334,7 +6334,7 @@
         <v>1002</v>
       </c>
       <c r="O101" t="n">
-        <v>14</v>
+        <v>14.0125</v>
       </c>
     </row>
     <row r="102">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>R$ 235.77</t>
+          <t>R$ 235,77</t>
         </is>
       </c>
       <c r="G102" t="inlineStr"/>
@@ -6371,7 +6371,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0</v>
+        <v>235.77</v>
       </c>
       <c r="J102" s="1" t="n">
         <v>46047</v>
@@ -6389,7 +6389,7 @@
         <v>1001</v>
       </c>
       <c r="O102" t="n">
-        <v>0</v>
+        <v>3.186081081081081</v>
       </c>
     </row>
     <row r="103">
@@ -6430,7 +6430,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>244</v>
+        <v>244.33</v>
       </c>
       <c r="J103" s="1" t="n">
         <v>46047</v>
@@ -6448,7 +6448,7 @@
         <v>1001</v>
       </c>
       <c r="O103" t="n">
-        <v>2.804597701149425</v>
+        <v>2.808390804597701</v>
       </c>
     </row>
     <row r="104">
@@ -6475,7 +6475,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>R$ 189.38</t>
+          <t>R$ 189,38</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -6489,7 +6489,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0</v>
+        <v>189.38</v>
       </c>
       <c r="J104" s="1" t="n">
         <v>46047</v>
@@ -6507,7 +6507,7 @@
         <v>1001</v>
       </c>
       <c r="O104" t="n">
-        <v>0</v>
+        <v>2.309512195121951</v>
       </c>
     </row>
     <row r="105">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>R$ 151.09</t>
+          <t>R$ 151,09</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -6548,7 +6548,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0</v>
+        <v>151.09</v>
       </c>
       <c r="J105" s="1" t="n">
         <v>46047</v>
@@ -6566,7 +6566,7 @@
         <v>1001</v>
       </c>
       <c r="O105" t="n">
-        <v>0</v>
+        <v>3.0218</v>
       </c>
     </row>
     <row r="106">
@@ -6607,7 +6607,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>209</v>
+        <v>209.08</v>
       </c>
       <c r="J106" s="1" t="n">
         <v>46047</v>
@@ -6625,7 +6625,7 @@
         <v>1001</v>
       </c>
       <c r="O106" t="n">
-        <v>2.824324324324324</v>
+        <v>2.825405405405406</v>
       </c>
     </row>
     <row r="107">
@@ -6666,7 +6666,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>913</v>
+        <v>913.3200000000001</v>
       </c>
       <c r="J107" s="1" t="n">
         <v>46048</v>
@@ -6684,7 +6684,7 @@
         <v>1002</v>
       </c>
       <c r="O107" t="n">
-        <v>22.26829268292683</v>
+        <v>22.27609756097561</v>
       </c>
     </row>
     <row r="108">
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>942</v>
+        <v>942.64</v>
       </c>
       <c r="J108" s="1" t="n">
         <v>46048</v>
@@ -6743,7 +6743,7 @@
         <v>1002</v>
       </c>
       <c r="O108" t="n">
-        <v>26.16666666666667</v>
+        <v>26.18444444444444</v>
       </c>
     </row>
     <row r="109">
@@ -6784,7 +6784,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>668</v>
+        <v>668.3</v>
       </c>
       <c r="J109" s="1" t="n">
         <v>46048</v>
@@ -6802,7 +6802,7 @@
         <v>1002</v>
       </c>
       <c r="O109" t="n">
-        <v>30.36363636363636</v>
+        <v>30.37727272727273</v>
       </c>
     </row>
     <row r="110">
@@ -6843,7 +6843,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1742</v>
+        <v>1742.08</v>
       </c>
       <c r="J110" s="1" t="n">
         <v>46048</v>
@@ -6861,7 +6861,7 @@
         <v>1002</v>
       </c>
       <c r="O110" t="n">
-        <v>34.84</v>
+        <v>34.8416</v>
       </c>
     </row>
     <row r="111">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>R$ 201.38</t>
+          <t>R$ 201,38</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -6902,7 +6902,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0</v>
+        <v>201.38</v>
       </c>
       <c r="J111" s="1" t="n">
         <v>46049</v>
@@ -6920,7 +6920,7 @@
         <v>1001</v>
       </c>
       <c r="O111" t="n">
-        <v>0</v>
+        <v>3.098153846153846</v>
       </c>
     </row>
     <row r="112">
@@ -6961,7 +6961,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>273</v>
+        <v>273.07</v>
       </c>
       <c r="J112" s="1" t="n">
         <v>46049</v>
@@ -6979,7 +6979,7 @@
         <v>1001</v>
       </c>
       <c r="O112" t="n">
-        <v>2.967391304347826</v>
+        <v>2.968152173913043</v>
       </c>
     </row>
     <row r="113">
@@ -7020,7 +7020,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>349</v>
+        <v>349.63</v>
       </c>
       <c r="J113" s="1" t="n">
         <v>46049</v>
@@ -7038,7 +7038,7 @@
         <v>1001</v>
       </c>
       <c r="O113" t="n">
-        <v>3.455445544554455</v>
+        <v>3.461683168316831</v>
       </c>
     </row>
     <row r="114">
@@ -7079,7 +7079,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>235</v>
+        <v>235.97</v>
       </c>
       <c r="J114" s="1" t="n">
         <v>46049</v>
@@ -7097,7 +7097,7 @@
         <v>1001</v>
       </c>
       <c r="O114" t="n">
-        <v>2.831325301204819</v>
+        <v>2.843012048192771</v>
       </c>
     </row>
     <row r="115">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>R$ 359.16</t>
+          <t>R$ 359,16</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -7138,7 +7138,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0</v>
+        <v>359.16</v>
       </c>
       <c r="J115" s="1" t="n">
         <v>46049</v>
@@ -7156,7 +7156,7 @@
         <v>1001</v>
       </c>
       <c r="O115" t="n">
-        <v>0</v>
+        <v>3.388301886792453</v>
       </c>
     </row>
     <row r="116">
@@ -7197,7 +7197,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>811</v>
+        <v>811.23</v>
       </c>
       <c r="J116" s="1" t="n">
         <v>46050</v>
@@ -7215,7 +7215,7 @@
         <v>1002</v>
       </c>
       <c r="O116" t="n">
-        <v>24.57575757575757</v>
+        <v>24.58272727272727</v>
       </c>
     </row>
     <row r="117">
@@ -7256,7 +7256,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>972</v>
+        <v>972.63</v>
       </c>
       <c r="J117" s="1" t="n">
         <v>46050</v>
@@ -7274,7 +7274,7 @@
         <v>1002</v>
       </c>
       <c r="O117" t="n">
-        <v>18.69230769230769</v>
+        <v>18.70442307692308</v>
       </c>
     </row>
     <row r="118">
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>786</v>
+        <v>786.52</v>
       </c>
       <c r="J118" s="1" t="n">
         <v>46050</v>
@@ -7333,7 +7333,7 @@
         <v>1002</v>
       </c>
       <c r="O118" t="n">
-        <v>28.07142857142857</v>
+        <v>28.09</v>
       </c>
     </row>
     <row r="119">
@@ -7374,7 +7374,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1232</v>
+        <v>1232.23</v>
       </c>
       <c r="J119" s="1" t="n">
         <v>46050</v>
@@ -7392,7 +7392,7 @@
         <v>1002</v>
       </c>
       <c r="O119" t="n">
-        <v>27.37777777777778</v>
+        <v>27.38288888888889</v>
       </c>
     </row>
     <row r="120">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>R$ 131.55</t>
+          <t>R$ 131,55</t>
         </is>
       </c>
       <c r="G120" t="inlineStr"/>
@@ -7429,7 +7429,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0</v>
+        <v>131.55</v>
       </c>
       <c r="J120" s="1" t="n">
         <v>46051</v>
@@ -7447,7 +7447,7 @@
         <v>1001</v>
       </c>
       <c r="O120" t="n">
-        <v>0</v>
+        <v>2.229661016949153</v>
       </c>
     </row>
     <row r="121">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>R$ 231.85</t>
+          <t>R$ 231,85</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -7488,7 +7488,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0</v>
+        <v>231.85</v>
       </c>
       <c r="J121" s="1" t="n">
         <v>46051</v>
@@ -7506,7 +7506,7 @@
         <v>1001</v>
       </c>
       <c r="O121" t="n">
-        <v>0</v>
+        <v>2.051769911504425</v>
       </c>
     </row>
     <row r="122">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>R$ 144.49</t>
+          <t>R$ 144,49</t>
         </is>
       </c>
       <c r="G122" t="inlineStr"/>
@@ -7543,7 +7543,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0</v>
+        <v>144.49</v>
       </c>
       <c r="J122" s="1" t="n">
         <v>46051</v>
@@ -7561,7 +7561,7 @@
         <v>1001</v>
       </c>
       <c r="O122" t="n">
-        <v>0</v>
+        <v>2.534912280701755</v>
       </c>
     </row>
     <row r="123">
@@ -7602,7 +7602,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>120</v>
+        <v>120.56</v>
       </c>
       <c r="J123" s="1" t="n">
         <v>46051</v>
@@ -7620,7 +7620,7 @@
         <v>1001</v>
       </c>
       <c r="O123" t="n">
-        <v>2.608695652173913</v>
+        <v>2.620869565217391</v>
       </c>
     </row>
     <row r="124">
@@ -7657,7 +7657,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>143</v>
+        <v>143.28</v>
       </c>
       <c r="J124" s="1" t="n">
         <v>46051</v>
@@ -7675,7 +7675,7 @@
         <v>1001</v>
       </c>
       <c r="O124" t="n">
-        <v>3.325581395348837</v>
+        <v>3.332093023255814</v>
       </c>
     </row>
     <row r="125">
@@ -7716,7 +7716,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>790</v>
+        <v>790.53</v>
       </c>
       <c r="J125" s="1" t="n">
         <v>46052</v>
@@ -7734,7 +7734,7 @@
         <v>1002</v>
       </c>
       <c r="O125" t="n">
-        <v>17.17391304347826</v>
+        <v>17.1854347826087</v>
       </c>
     </row>
     <row r="126">
@@ -7775,7 +7775,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>732</v>
+        <v>732.54</v>
       </c>
       <c r="J126" s="1" t="n">
         <v>46052</v>
@@ -7793,7 +7793,7 @@
         <v>1002</v>
       </c>
       <c r="O126" t="n">
-        <v>14.07692307692308</v>
+        <v>14.08730769230769</v>
       </c>
     </row>
     <row r="127">
@@ -7834,7 +7834,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>585</v>
+        <v>585.8200000000001</v>
       </c>
       <c r="J127" s="1" t="n">
         <v>46052</v>
@@ -7852,7 +7852,7 @@
         <v>1002</v>
       </c>
       <c r="O127" t="n">
-        <v>22.5</v>
+        <v>22.53153846153846</v>
       </c>
     </row>
     <row r="128">
@@ -7893,7 +7893,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>365</v>
+        <v>365.88</v>
       </c>
       <c r="J128" s="1" t="n">
         <v>46052</v>
@@ -7911,7 +7911,7 @@
         <v>1002</v>
       </c>
       <c r="O128" t="n">
-        <v>17.38095238095238</v>
+        <v>17.42285714285714</v>
       </c>
     </row>
     <row r="129">
@@ -7938,7 +7938,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>R$ 306.7</t>
+          <t>R$ 306,7</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -7952,7 +7952,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0</v>
+        <v>306.7</v>
       </c>
       <c r="J129" s="1" t="n">
         <v>46053</v>
@@ -7970,7 +7970,7 @@
         <v>1001</v>
       </c>
       <c r="O129" t="n">
-        <v>0</v>
+        <v>3.262765957446808</v>
       </c>
     </row>
     <row r="130">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>221</v>
+        <v>221.47</v>
       </c>
       <c r="J130" s="1" t="n">
         <v>46053</v>
@@ -8029,7 +8029,7 @@
         <v>1001</v>
       </c>
       <c r="O130" t="n">
-        <v>3.298507462686567</v>
+        <v>3.305522388059702</v>
       </c>
     </row>
     <row r="131">
@@ -8070,7 +8070,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>175</v>
+        <v>175.61</v>
       </c>
       <c r="J131" s="1" t="n">
         <v>46053</v>
@@ -8088,7 +8088,7 @@
         <v>1001</v>
       </c>
       <c r="O131" t="n">
-        <v>2.651515151515151</v>
+        <v>2.660757575757576</v>
       </c>
     </row>
     <row r="132">
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>141</v>
+        <v>141.92</v>
       </c>
       <c r="J132" s="1" t="n">
         <v>46053</v>
@@ -8143,7 +8143,7 @@
         <v>1001</v>
       </c>
       <c r="O132" t="n">
-        <v>2.104477611940299</v>
+        <v>2.118208955223881</v>
       </c>
     </row>
     <row r="133">
@@ -8170,7 +8170,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>R$ 159.02</t>
+          <t>R$ 159,02</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -8184,7 +8184,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0</v>
+        <v>159.02</v>
       </c>
       <c r="J133" s="1" t="n">
         <v>46053</v>
@@ -8202,7 +8202,7 @@
         <v>1001</v>
       </c>
       <c r="O133" t="n">
-        <v>0</v>
+        <v>2.650333333333334</v>
       </c>
     </row>
     <row r="134">
@@ -8243,7 +8243,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>149</v>
+        <v>149.06</v>
       </c>
       <c r="J134" s="1" t="n">
         <v>46055</v>
@@ -8261,7 +8261,7 @@
         <v>1001</v>
       </c>
       <c r="O134" t="n">
-        <v>2.013513513513514</v>
+        <v>2.014324324324325</v>
       </c>
     </row>
     <row r="135">
@@ -8288,7 +8288,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>R$ 271.15</t>
+          <t>R$ 271,15</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0</v>
+        <v>271.15</v>
       </c>
       <c r="J135" s="1" t="n">
         <v>46055</v>
@@ -8320,7 +8320,7 @@
         <v>1001</v>
       </c>
       <c r="O135" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="136">
@@ -8361,7 +8361,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>203</v>
+        <v>203.09</v>
       </c>
       <c r="J136" s="1" t="n">
         <v>46055</v>
@@ -8379,7 +8379,7 @@
         <v>1001</v>
       </c>
       <c r="O136" t="n">
-        <v>2.071428571428572</v>
+        <v>2.07234693877551</v>
       </c>
     </row>
     <row r="137">
@@ -8420,7 +8420,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>194</v>
+        <v>194.6</v>
       </c>
       <c r="J137" s="1" t="n">
         <v>46055</v>
@@ -8438,7 +8438,7 @@
         <v>1001</v>
       </c>
       <c r="O137" t="n">
-        <v>2.694444444444445</v>
+        <v>2.702777777777778</v>
       </c>
     </row>
     <row r="138">
@@ -8479,7 +8479,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>261</v>
+        <v>261.63</v>
       </c>
       <c r="J138" s="1" t="n">
         <v>46055</v>
@@ -8497,7 +8497,7 @@
         <v>1001</v>
       </c>
       <c r="O138" t="n">
-        <v>2.439252336448598</v>
+        <v>2.445140186915888</v>
       </c>
     </row>
     <row r="139">
@@ -8538,7 +8538,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2009</v>
+        <v>2009.19</v>
       </c>
       <c r="J139" s="1" t="n">
         <v>46055</v>
@@ -8556,7 +8556,7 @@
         <v>1002</v>
       </c>
       <c r="O139" t="n">
-        <v>37.90566037735849</v>
+        <v>37.90924528301887</v>
       </c>
     </row>
     <row r="140">
@@ -8597,7 +8597,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1521</v>
+        <v>1521.37</v>
       </c>
       <c r="J140" s="1" t="n">
         <v>46055</v>
@@ -8615,7 +8615,7 @@
         <v>1002</v>
       </c>
       <c r="O140" t="n">
-        <v>34.56818181818182</v>
+        <v>34.5765909090909</v>
       </c>
     </row>
     <row r="141">
@@ -8656,7 +8656,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1529</v>
+        <v>1529.46</v>
       </c>
       <c r="J141" s="1" t="n">
         <v>46055</v>
@@ -8674,7 +8674,7 @@
         <v>1002</v>
       </c>
       <c r="O141" t="n">
-        <v>25.91525423728813</v>
+        <v>25.92305084745763</v>
       </c>
     </row>
     <row r="142">
@@ -8715,7 +8715,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>665</v>
+        <v>665.0700000000001</v>
       </c>
       <c r="J142" s="1" t="n">
         <v>46055</v>
@@ -8733,7 +8733,7 @@
         <v>1002</v>
       </c>
       <c r="O142" t="n">
-        <v>16.625</v>
+        <v>16.62675</v>
       </c>
     </row>
     <row r="143">
@@ -8774,7 +8774,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>103</v>
+        <v>103.4</v>
       </c>
       <c r="J143" s="1" t="n">
         <v>46057</v>
@@ -8792,7 +8792,7 @@
         <v>1001</v>
       </c>
       <c r="O143" t="n">
-        <v>2.019607843137255</v>
+        <v>2.027450980392157</v>
       </c>
     </row>
     <row r="144">
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>384</v>
+        <v>384.32</v>
       </c>
       <c r="J144" s="1" t="n">
         <v>46057</v>
@@ -8851,7 +8851,7 @@
         <v>1001</v>
       </c>
       <c r="O144" t="n">
-        <v>3.282051282051282</v>
+        <v>3.284786324786325</v>
       </c>
     </row>
     <row r="145">
@@ -8892,7 +8892,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>270</v>
+        <v>270.3</v>
       </c>
       <c r="J145" s="1" t="n">
         <v>46057</v>
@@ -8910,7 +8910,7 @@
         <v>1001</v>
       </c>
       <c r="O145" t="n">
-        <v>2.7</v>
+        <v>2.703</v>
       </c>
     </row>
     <row r="146">
@@ -8937,7 +8937,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>R$ 231.48</t>
+          <t>R$ 231,48</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0</v>
+        <v>231.48</v>
       </c>
       <c r="J146" s="1" t="n">
         <v>46057</v>
@@ -8969,7 +8969,7 @@
         <v>1001</v>
       </c>
       <c r="O146" t="n">
-        <v>0</v>
+        <v>2.8935</v>
       </c>
     </row>
     <row r="147">
@@ -9010,7 +9010,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>321</v>
+        <v>321.41</v>
       </c>
       <c r="J147" s="1" t="n">
         <v>46057</v>
@@ -9028,7 +9028,7 @@
         <v>1001</v>
       </c>
       <c r="O147" t="n">
-        <v>2.791304347826087</v>
+        <v>2.794869565217391</v>
       </c>
     </row>
     <row r="148">
@@ -9069,7 +9069,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>600</v>
+        <v>600.55</v>
       </c>
       <c r="J148" s="1" t="n">
         <v>46057</v>
@@ -9087,7 +9087,7 @@
         <v>1002</v>
       </c>
       <c r="O148" t="n">
-        <v>27.27272727272727</v>
+        <v>27.29772727272727</v>
       </c>
     </row>
     <row r="149">
@@ -9128,7 +9128,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1268</v>
+        <v>1268.25</v>
       </c>
       <c r="J149" s="1" t="n">
         <v>46057</v>
@@ -9146,7 +9146,7 @@
         <v>1002</v>
       </c>
       <c r="O149" t="n">
-        <v>36.22857142857143</v>
+        <v>36.23571428571429</v>
       </c>
     </row>
     <row r="150">
@@ -9187,7 +9187,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1706</v>
+        <v>1706.95</v>
       </c>
       <c r="J150" s="1" t="n">
         <v>46057</v>
@@ -9205,7 +9205,7 @@
         <v>1002</v>
       </c>
       <c r="O150" t="n">
-        <v>36.29787234042553</v>
+        <v>36.31808510638298</v>
       </c>
     </row>
     <row r="151">
@@ -9246,7 +9246,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1228</v>
+        <v>1228.91</v>
       </c>
       <c r="J151" s="1" t="n">
         <v>46057</v>
@@ -9264,7 +9264,7 @@
         <v>1002</v>
       </c>
       <c r="O151" t="n">
-        <v>29.23809523809524</v>
+        <v>29.25976190476191</v>
       </c>
     </row>
     <row r="152">
@@ -9305,7 +9305,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>248</v>
+        <v>248.8</v>
       </c>
       <c r="J152" s="1" t="n">
         <v>46059</v>
@@ -9323,7 +9323,7 @@
         <v>1001</v>
       </c>
       <c r="O152" t="n">
-        <v>2.317757009345794</v>
+        <v>2.325233644859813</v>
       </c>
     </row>
     <row r="153">
@@ -9364,7 +9364,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>291</v>
+        <v>291.91</v>
       </c>
       <c r="J153" s="1" t="n">
         <v>46059</v>
@@ -9382,7 +9382,7 @@
         <v>1001</v>
       </c>
       <c r="O153" t="n">
-        <v>3.197802197802198</v>
+        <v>3.207802197802198</v>
       </c>
     </row>
     <row r="154">
@@ -9409,7 +9409,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>R$ 227.24</t>
+          <t>R$ 227,24</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -9423,7 +9423,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0</v>
+        <v>227.24</v>
       </c>
       <c r="J154" s="1" t="n">
         <v>46059</v>
@@ -9441,7 +9441,7 @@
         <v>1001</v>
       </c>
       <c r="O154" t="n">
-        <v>0</v>
+        <v>3.20056338028169</v>
       </c>
     </row>
     <row r="155">
@@ -9478,7 +9478,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>102</v>
+        <v>102.73</v>
       </c>
       <c r="J155" s="1" t="n">
         <v>46059</v>
@@ -9496,7 +9496,7 @@
         <v>1001</v>
       </c>
       <c r="O155" t="n">
-        <v>2.04</v>
+        <v>2.0546</v>
       </c>
     </row>
     <row r="156">
@@ -9533,7 +9533,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>333</v>
+        <v>333.06</v>
       </c>
       <c r="J156" s="1" t="n">
         <v>46059</v>
@@ -9551,7 +9551,7 @@
         <v>1001</v>
       </c>
       <c r="O156" t="n">
-        <v>3</v>
+        <v>3.000540540540541</v>
       </c>
     </row>
     <row r="157">
@@ -9592,7 +9592,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1749</v>
+        <v>1749.51</v>
       </c>
       <c r="J157" s="1" t="n">
         <v>46059</v>
@@ -9610,7 +9610,7 @@
         <v>1002</v>
       </c>
       <c r="O157" t="n">
-        <v>35.69387755102041</v>
+        <v>35.70428571428572</v>
       </c>
     </row>
     <row r="158">
@@ -9651,7 +9651,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>977</v>
+        <v>977.97</v>
       </c>
       <c r="J158" s="1" t="n">
         <v>46059</v>
@@ -9669,7 +9669,7 @@
         <v>1002</v>
       </c>
       <c r="O158" t="n">
-        <v>30.53125</v>
+        <v>30.5615625</v>
       </c>
     </row>
     <row r="159">
@@ -9710,7 +9710,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>587</v>
+        <v>587.46</v>
       </c>
       <c r="J159" s="1" t="n">
         <v>46059</v>
@@ -9728,7 +9728,7 @@
         <v>1002</v>
       </c>
       <c r="O159" t="n">
-        <v>15.44736842105263</v>
+        <v>15.45947368421053</v>
       </c>
     </row>
     <row r="160">
@@ -9769,7 +9769,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>685</v>
+        <v>685.4</v>
       </c>
       <c r="J160" s="1" t="n">
         <v>46059</v>
@@ -9787,7 +9787,7 @@
         <v>1002</v>
       </c>
       <c r="O160" t="n">
-        <v>18.51351351351351</v>
+        <v>18.52432432432432</v>
       </c>
     </row>
     <row r="161">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>R$ 305.11</t>
+          <t>R$ 305,11</t>
         </is>
       </c>
       <c r="G161" t="inlineStr"/>
@@ -9824,7 +9824,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0</v>
+        <v>305.11</v>
       </c>
       <c r="J161" s="1" t="n">
         <v>46061</v>
@@ -9842,7 +9842,7 @@
         <v>1001</v>
       </c>
       <c r="O161" t="n">
-        <v>0</v>
+        <v>3.0511</v>
       </c>
     </row>
     <row r="162">
@@ -9883,7 +9883,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>342</v>
+        <v>342.41</v>
       </c>
       <c r="J162" s="1" t="n">
         <v>46061</v>
@@ -9901,7 +9901,7 @@
         <v>1001</v>
       </c>
       <c r="O162" t="n">
-        <v>3.226415094339623</v>
+        <v>3.230283018867925</v>
       </c>
     </row>
     <row r="163">
@@ -9942,7 +9942,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>182</v>
+        <v>182.04</v>
       </c>
       <c r="J163" s="1" t="n">
         <v>46061</v>
@@ -9960,7 +9960,7 @@
         <v>1001</v>
       </c>
       <c r="O163" t="n">
-        <v>2.022222222222222</v>
+        <v>2.022666666666666</v>
       </c>
     </row>
     <row r="164">
@@ -10001,7 +10001,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>337</v>
+        <v>337.81</v>
       </c>
       <c r="J164" s="1" t="n">
         <v>46061</v>
@@ -10019,7 +10019,7 @@
         <v>1001</v>
       </c>
       <c r="O164" t="n">
-        <v>2.831932773109244</v>
+        <v>2.838739495798319</v>
       </c>
     </row>
     <row r="165">
@@ -10056,7 +10056,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>202</v>
+        <v>202.66</v>
       </c>
       <c r="J165" s="1" t="n">
         <v>46061</v>
@@ -10074,7 +10074,7 @@
         <v>1001</v>
       </c>
       <c r="O165" t="n">
-        <v>2.693333333333333</v>
+        <v>2.702133333333333</v>
       </c>
     </row>
     <row r="166">
@@ -10115,7 +10115,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1105</v>
+        <v>1105.61</v>
       </c>
       <c r="J166" s="1" t="n">
         <v>46062</v>
@@ -10133,7 +10133,7 @@
         <v>1002</v>
       </c>
       <c r="O166" t="n">
-        <v>39.46428571428572</v>
+        <v>39.48607142857143</v>
       </c>
     </row>
     <row r="167">
@@ -10174,7 +10174,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1825</v>
+        <v>1825.27</v>
       </c>
       <c r="J167" s="1" t="n">
         <v>46062</v>
@@ -10192,7 +10192,7 @@
         <v>1002</v>
       </c>
       <c r="O167" t="n">
-        <v>36.5</v>
+        <v>36.5054</v>
       </c>
     </row>
     <row r="168">
@@ -10233,7 +10233,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>817</v>
+        <v>817.3</v>
       </c>
       <c r="J168" s="1" t="n">
         <v>46062</v>
@@ -10251,7 +10251,7 @@
         <v>1002</v>
       </c>
       <c r="O168" t="n">
-        <v>26.35483870967742</v>
+        <v>26.36451612903226</v>
       </c>
     </row>
     <row r="169">
@@ -10292,7 +10292,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>699</v>
+        <v>699.78</v>
       </c>
       <c r="J169" s="1" t="n">
         <v>46062</v>
@@ -10310,7 +10310,7 @@
         <v>1002</v>
       </c>
       <c r="O169" t="n">
-        <v>34.95</v>
+        <v>34.989</v>
       </c>
     </row>
     <row r="170">
@@ -10337,7 +10337,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>R$ 332.22</t>
+          <t>R$ 332,22</t>
         </is>
       </c>
       <c r="G170" t="inlineStr"/>
@@ -10347,7 +10347,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0</v>
+        <v>332.22</v>
       </c>
       <c r="J170" s="1" t="n">
         <v>46063</v>
@@ -10365,7 +10365,7 @@
         <v>1001</v>
       </c>
       <c r="O170" t="n">
-        <v>0</v>
+        <v>2.7685</v>
       </c>
     </row>
     <row r="171">
@@ -10406,7 +10406,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>273</v>
+        <v>273.52</v>
       </c>
       <c r="J171" s="1" t="n">
         <v>46063</v>
@@ -10424,7 +10424,7 @@
         <v>1001</v>
       </c>
       <c r="O171" t="n">
-        <v>-2.373913043478261</v>
+        <v>-2.378434782608696</v>
       </c>
     </row>
     <row r="172">
@@ -10465,7 +10465,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>272</v>
+        <v>272.28</v>
       </c>
       <c r="J172" s="1" t="n">
         <v>46063</v>
@@ -10483,7 +10483,7 @@
         <v>1001</v>
       </c>
       <c r="O172" t="n">
-        <v>3.487179487179487</v>
+        <v>3.490769230769231</v>
       </c>
     </row>
     <row r="173">
@@ -10524,7 +10524,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>127</v>
+        <v>127.28</v>
       </c>
       <c r="J173" s="1" t="n">
         <v>46063</v>
@@ -10542,7 +10542,7 @@
         <v>1001</v>
       </c>
       <c r="O173" t="n">
-        <v>3.097560975609756</v>
+        <v>3.104390243902439</v>
       </c>
     </row>
     <row r="174">
@@ -10583,7 +10583,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>158</v>
+        <v>158.95</v>
       </c>
       <c r="J174" s="1" t="n">
         <v>46063</v>
@@ -10601,7 +10601,7 @@
         <v>1001</v>
       </c>
       <c r="O174" t="n">
-        <v>2.225352112676056</v>
+        <v>2.238732394366197</v>
       </c>
     </row>
     <row r="175">
@@ -10642,7 +10642,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>400</v>
+        <v>400.22</v>
       </c>
       <c r="J175" s="1" t="n">
         <v>46064</v>
@@ -10660,7 +10660,7 @@
         <v>1002</v>
       </c>
       <c r="O175" t="n">
-        <v>14.81481481481481</v>
+        <v>14.82296296296296</v>
       </c>
     </row>
     <row r="176">
@@ -10701,7 +10701,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>696</v>
+        <v>696.24</v>
       </c>
       <c r="J176" s="1" t="n">
         <v>46064</v>
@@ -10719,7 +10719,7 @@
         <v>1002</v>
       </c>
       <c r="O176" t="n">
-        <v>24</v>
+        <v>24.00827586206897</v>
       </c>
     </row>
     <row r="177">
@@ -10760,7 +10760,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1412</v>
+        <v>1412.64</v>
       </c>
       <c r="J177" s="1" t="n">
         <v>46064</v>
@@ -10778,7 +10778,7 @@
         <v>1002</v>
       </c>
       <c r="O177" t="n">
-        <v>29.41666666666667</v>
+        <v>29.43</v>
       </c>
     </row>
     <row r="178">
@@ -10819,7 +10819,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1793</v>
+        <v>1793.07</v>
       </c>
       <c r="J178" s="1" t="n">
         <v>46064</v>
@@ -10837,7 +10837,7 @@
         <v>1002</v>
       </c>
       <c r="O178" t="n">
-        <v>29.88333333333333</v>
+        <v>29.8845</v>
       </c>
     </row>
     <row r="179">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>167</v>
+        <v>167.16</v>
       </c>
       <c r="J179" s="1" t="n">
         <v>46065</v>
@@ -10896,7 +10896,7 @@
         <v>1001</v>
       </c>
       <c r="O179" t="n">
-        <v>3.211538461538462</v>
+        <v>3.214615384615385</v>
       </c>
     </row>
     <row r="180">
@@ -10937,7 +10937,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>228</v>
+        <v>228.13</v>
       </c>
       <c r="J180" s="1" t="n">
         <v>46065</v>
@@ -10955,7 +10955,7 @@
         <v>1001</v>
       </c>
       <c r="O180" t="n">
-        <v>2.375</v>
+        <v>2.376354166666667</v>
       </c>
     </row>
     <row r="181">
@@ -10982,7 +10982,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>R$ 165.74</t>
+          <t>R$ 165,74</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -10996,7 +10996,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>0</v>
+        <v>165.74</v>
       </c>
       <c r="J181" s="1" t="n">
         <v>46065</v>
@@ -11014,7 +11014,7 @@
         <v>1001</v>
       </c>
       <c r="O181" t="n">
-        <v>0</v>
+        <v>2.152467532467532</v>
       </c>
     </row>
     <row r="182">
@@ -11055,7 +11055,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>200</v>
+        <v>200.59</v>
       </c>
       <c r="J182" s="1" t="n">
         <v>46065</v>
@@ -11073,7 +11073,7 @@
         <v>1001</v>
       </c>
       <c r="O182" t="n">
-        <v>2.597402597402597</v>
+        <v>2.605064935064935</v>
       </c>
     </row>
     <row r="183">
@@ -11114,7 +11114,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>130</v>
+        <v>130.15</v>
       </c>
       <c r="J183" s="1" t="n">
         <v>46065</v>
@@ -11132,7 +11132,7 @@
         <v>1001</v>
       </c>
       <c r="O183" t="n">
-        <v>2.5</v>
+        <v>2.502884615384616</v>
       </c>
     </row>
     <row r="184">
@@ -11173,7 +11173,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>1164</v>
+        <v>1164.78</v>
       </c>
       <c r="J184" s="1" t="n">
         <v>46066</v>
@@ -11191,7 +11191,7 @@
         <v>1002</v>
       </c>
       <c r="O184" t="n">
-        <v>21.16363636363636</v>
+        <v>21.17781818181818</v>
       </c>
     </row>
     <row r="185">
@@ -11232,7 +11232,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>805</v>
+        <v>805.9</v>
       </c>
       <c r="J185" s="1" t="n">
         <v>46066</v>
@@ -11250,7 +11250,7 @@
         <v>1002</v>
       </c>
       <c r="O185" t="n">
-        <v>22.36111111111111</v>
+        <v>22.38611111111111</v>
       </c>
     </row>
     <row r="186">
@@ -11291,7 +11291,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>828</v>
+        <v>828.76</v>
       </c>
       <c r="J186" s="1" t="n">
         <v>46066</v>
@@ -11309,7 +11309,7 @@
         <v>1002</v>
       </c>
       <c r="O186" t="n">
-        <v>26.70967741935484</v>
+        <v>26.7341935483871</v>
       </c>
     </row>
     <row r="187">
@@ -11350,7 +11350,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>685</v>
+        <v>685.84</v>
       </c>
       <c r="J187" s="1" t="n">
         <v>46066</v>
@@ -11368,7 +11368,7 @@
         <v>1002</v>
       </c>
       <c r="O187" t="n">
-        <v>17.56410256410257</v>
+        <v>17.58564102564103</v>
       </c>
     </row>
     <row r="188">
@@ -11409,7 +11409,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>290</v>
+        <v>290.05</v>
       </c>
       <c r="J188" s="1" t="n">
         <v>46067</v>
@@ -11427,7 +11427,7 @@
         <v>1001</v>
       </c>
       <c r="O188" t="n">
-        <v>3.020833333333333</v>
+        <v>3.021354166666667</v>
       </c>
     </row>
     <row r="189">
@@ -11464,7 +11464,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>377</v>
+        <v>377.54</v>
       </c>
       <c r="J189" s="1" t="n">
         <v>46067</v>
@@ -11482,7 +11482,7 @@
         <v>1001</v>
       </c>
       <c r="O189" t="n">
-        <v>3.25</v>
+        <v>3.254655172413793</v>
       </c>
     </row>
     <row r="190">
@@ -11523,7 +11523,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>298</v>
+        <v>298.76</v>
       </c>
       <c r="J190" s="1" t="n">
         <v>46067</v>
@@ -11541,7 +11541,7 @@
         <v>1001</v>
       </c>
       <c r="O190" t="n">
-        <v>2.759259259259259</v>
+        <v>2.766296296296296</v>
       </c>
     </row>
     <row r="191">
@@ -11568,7 +11568,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>R$ 325.19</t>
+          <t>R$ 325,19</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -11582,7 +11582,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>0</v>
+        <v>325.19</v>
       </c>
       <c r="J191" s="1" t="n">
         <v>46067</v>
@@ -11600,7 +11600,7 @@
         <v>1001</v>
       </c>
       <c r="O191" t="n">
-        <v>0</v>
+        <v>3.126826923076923</v>
       </c>
     </row>
     <row r="192">
@@ -11641,7 +11641,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>359</v>
+        <v>359.98</v>
       </c>
       <c r="J192" s="1" t="n">
         <v>46067</v>
@@ -11659,7 +11659,7 @@
         <v>1001</v>
       </c>
       <c r="O192" t="n">
-        <v>3.355140186915888</v>
+        <v>3.364299065420561</v>
       </c>
     </row>
     <row r="193">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>R$ 173.72</t>
+          <t>R$ 173,72</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -11700,7 +11700,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>0</v>
+        <v>173.72</v>
       </c>
       <c r="J193" s="1" t="n">
         <v>46069</v>
@@ -11718,7 +11718,7 @@
         <v>1001</v>
       </c>
       <c r="O193" t="n">
-        <v>0</v>
+        <v>2.043764705882353</v>
       </c>
     </row>
     <row r="194">
@@ -11745,7 +11745,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>R$ 266.08</t>
+          <t>R$ 266,08</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -11759,7 +11759,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>0</v>
+        <v>266.08</v>
       </c>
       <c r="J194" s="1" t="n">
         <v>46069</v>
@@ -11777,7 +11777,7 @@
         <v>1001</v>
       </c>
       <c r="O194" t="n">
-        <v>0</v>
+        <v>2.235966386554622</v>
       </c>
     </row>
     <row r="195">
@@ -11818,7 +11818,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>253</v>
+        <v>253.54</v>
       </c>
       <c r="J195" s="1" t="n">
         <v>46069</v>
@@ -11836,7 +11836,7 @@
         <v>1001</v>
       </c>
       <c r="O195" t="n">
-        <v>2.321100917431193</v>
+        <v>2.32605504587156</v>
       </c>
     </row>
     <row r="196">
@@ -11877,7 +11877,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>278</v>
+        <v>278.2</v>
       </c>
       <c r="J196" s="1" t="n">
         <v>46069</v>
@@ -11895,7 +11895,7 @@
         <v>1001</v>
       </c>
       <c r="O196" t="n">
-        <v>2.622641509433962</v>
+        <v>2.624528301886792</v>
       </c>
     </row>
     <row r="197">
@@ -11936,7 +11936,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>155</v>
+        <v>155.39</v>
       </c>
       <c r="J197" s="1" t="n">
         <v>46069</v>
@@ -11954,7 +11954,7 @@
         <v>1001</v>
       </c>
       <c r="O197" t="n">
-        <v>2.980769230769231</v>
+        <v>2.988269230769231</v>
       </c>
     </row>
     <row r="198">
@@ -11995,7 +11995,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>918</v>
+        <v>918.37</v>
       </c>
       <c r="J198" s="1" t="n">
         <v>46069</v>
@@ -12013,7 +12013,7 @@
         <v>1002</v>
       </c>
       <c r="O198" t="n">
-        <v>35.30769230769231</v>
+        <v>35.32192307692308</v>
       </c>
     </row>
     <row r="199">
@@ -12054,7 +12054,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1191</v>
+        <v>1191.05</v>
       </c>
       <c r="J199" s="1" t="n">
         <v>46069</v>
@@ -12072,7 +12072,7 @@
         <v>1002</v>
       </c>
       <c r="O199" t="n">
-        <v>29.04878048780488</v>
+        <v>29.05</v>
       </c>
     </row>
     <row r="200">
@@ -12113,7 +12113,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>814</v>
+        <v>814.41</v>
       </c>
       <c r="J200" s="1" t="n">
         <v>46069</v>
@@ -12131,7 +12131,7 @@
         <v>1002</v>
       </c>
       <c r="O200" t="n">
-        <v>19.38095238095238</v>
+        <v>19.39071428571429</v>
       </c>
     </row>
     <row r="201">
@@ -12172,7 +12172,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>982</v>
+        <v>982.54</v>
       </c>
       <c r="J201" s="1" t="n">
         <v>46069</v>
@@ -12190,7 +12190,7 @@
         <v>1002</v>
       </c>
       <c r="O201" t="n">
-        <v>37.76923076923077</v>
+        <v>37.79</v>
       </c>
     </row>
     <row r="202">
@@ -12231,7 +12231,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>147</v>
+        <v>147.54</v>
       </c>
       <c r="J202" s="1" t="n">
         <v>46071</v>
@@ -12249,7 +12249,7 @@
         <v>1001</v>
       </c>
       <c r="O202" t="n">
-        <v>2.625</v>
+        <v>2.634642857142857</v>
       </c>
     </row>
     <row r="203">
@@ -12276,7 +12276,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>R$ 339.17</t>
+          <t>R$ 339,17</t>
         </is>
       </c>
       <c r="G203" t="inlineStr"/>
@@ -12286,7 +12286,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>0</v>
+        <v>339.17</v>
       </c>
       <c r="J203" s="1" t="n">
         <v>46071</v>
@@ -12304,7 +12304,7 @@
         <v>1001</v>
       </c>
       <c r="O203" t="n">
-        <v>0</v>
+        <v>3.49659793814433</v>
       </c>
     </row>
     <row r="204">
@@ -12345,7 +12345,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>113</v>
+        <v>113.86</v>
       </c>
       <c r="J204" s="1" t="n">
         <v>46071</v>
@@ -12363,7 +12363,7 @@
         <v>1001</v>
       </c>
       <c r="O204" t="n">
-        <v>2.354166666666667</v>
+        <v>2.372083333333333</v>
       </c>
     </row>
     <row r="205">
@@ -12404,7 +12404,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>130</v>
+        <v>130.66</v>
       </c>
       <c r="J205" s="1" t="n">
         <v>46071</v>
@@ -12422,7 +12422,7 @@
         <v>1001</v>
       </c>
       <c r="O205" t="n">
-        <v>3.170731707317073</v>
+        <v>3.186829268292683</v>
       </c>
     </row>
     <row r="206">
@@ -12463,7 +12463,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>165</v>
+        <v>165.82</v>
       </c>
       <c r="J206" s="1" t="n">
         <v>46071</v>
@@ -12481,7 +12481,7 @@
         <v>1001</v>
       </c>
       <c r="O206" t="n">
-        <v>3.113207547169811</v>
+        <v>3.128679245283019</v>
       </c>
     </row>
     <row r="207">
@@ -12522,7 +12522,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>1889</v>
+        <v>1889.69</v>
       </c>
       <c r="J207" s="1" t="n">
         <v>46071</v>
@@ -12540,7 +12540,7 @@
         <v>1002</v>
       </c>
       <c r="O207" t="n">
-        <v>33.73214285714285</v>
+        <v>33.74446428571429</v>
       </c>
     </row>
     <row r="208">
@@ -12581,7 +12581,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>1699</v>
+        <v>1699.6</v>
       </c>
       <c r="J208" s="1" t="n">
         <v>46071</v>
@@ -12599,7 +12599,7 @@
         <v>1002</v>
       </c>
       <c r="O208" t="n">
-        <v>36.14893617021276</v>
+        <v>36.16170212765957</v>
       </c>
     </row>
     <row r="209">
@@ -12640,7 +12640,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>1122</v>
+        <v>1122.82</v>
       </c>
       <c r="J209" s="1" t="n">
         <v>46071</v>
@@ -12658,7 +12658,7 @@
         <v>1002</v>
       </c>
       <c r="O209" t="n">
-        <v>33</v>
+        <v>33.02411764705882</v>
       </c>
     </row>
     <row r="210">
@@ -12699,7 +12699,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>1288</v>
+        <v>1288.68</v>
       </c>
       <c r="J210" s="1" t="n">
         <v>46071</v>
@@ -12717,7 +12717,7 @@
         <v>1002</v>
       </c>
       <c r="O210" t="n">
-        <v>24.30188679245283</v>
+        <v>24.31471698113208</v>
       </c>
     </row>
     <row r="211">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>R$ 350.79</t>
+          <t>R$ 350,79</t>
         </is>
       </c>
       <c r="G211" t="inlineStr"/>
@@ -12754,7 +12754,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>0</v>
+        <v>350.79</v>
       </c>
       <c r="J211" s="1" t="n">
         <v>46073</v>
@@ -12772,7 +12772,7 @@
         <v>1001</v>
       </c>
       <c r="O211" t="n">
-        <v>0</v>
+        <v>3.278411214953271</v>
       </c>
     </row>
     <row r="212">
@@ -12813,7 +12813,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>319</v>
+        <v>319.22</v>
       </c>
       <c r="J212" s="1" t="n">
         <v>46073</v>
@@ -12831,7 +12831,7 @@
         <v>1001</v>
       </c>
       <c r="O212" t="n">
-        <v>2.773913043478261</v>
+        <v>2.775826086956522</v>
       </c>
     </row>
     <row r="213">
@@ -12872,7 +12872,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>163</v>
+        <v>163.1</v>
       </c>
       <c r="J213" s="1" t="n">
         <v>46073</v>
@@ -12890,7 +12890,7 @@
         <v>1001</v>
       </c>
       <c r="O213" t="n">
-        <v>-2.295774647887324</v>
+        <v>-2.297183098591549</v>
       </c>
     </row>
     <row r="214">
@@ -12927,7 +12927,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>145</v>
+        <v>145.01</v>
       </c>
       <c r="J214" s="1" t="n">
         <v>46073</v>
@@ -12945,7 +12945,7 @@
         <v>1001</v>
       </c>
       <c r="O214" t="n">
-        <v>2.636363636363636</v>
+        <v>2.636545454545455</v>
       </c>
     </row>
     <row r="215">
@@ -12986,7 +12986,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>184</v>
+        <v>184.92</v>
       </c>
       <c r="J215" s="1" t="n">
         <v>46073</v>
@@ -13004,7 +13004,7 @@
         <v>1001</v>
       </c>
       <c r="O215" t="n">
-        <v>3.471698113207547</v>
+        <v>3.489056603773585</v>
       </c>
     </row>
     <row r="216">
@@ -13045,7 +13045,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>1134</v>
+        <v>1134.95</v>
       </c>
       <c r="J216" s="1" t="n">
         <v>46073</v>
@@ -13063,7 +13063,7 @@
         <v>1002</v>
       </c>
       <c r="O216" t="n">
-        <v>28.35</v>
+        <v>28.37375</v>
       </c>
     </row>
     <row r="217">
@@ -13104,7 +13104,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>984</v>
+        <v>984.12</v>
       </c>
       <c r="J217" s="1" t="n">
         <v>46073</v>
@@ -13122,7 +13122,7 @@
         <v>1002</v>
       </c>
       <c r="O217" t="n">
-        <v>23.42857142857143</v>
+        <v>23.43142857142857</v>
       </c>
     </row>
     <row r="218">
@@ -13163,7 +13163,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>663</v>
+        <v>663.53</v>
       </c>
       <c r="J218" s="1" t="n">
         <v>46073</v>
@@ -13181,7 +13181,7 @@
         <v>1002</v>
       </c>
       <c r="O218" t="n">
-        <v>13.26</v>
+        <v>13.2706</v>
       </c>
     </row>
     <row r="219">
@@ -13222,7 +13222,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>644</v>
+        <v>644.29</v>
       </c>
       <c r="J219" s="1" t="n">
         <v>46073</v>
@@ -13240,7 +13240,7 @@
         <v>1002</v>
       </c>
       <c r="O219" t="n">
-        <v>29.27272727272727</v>
+        <v>29.28590909090909</v>
       </c>
     </row>
     <row r="220">
@@ -13267,7 +13267,7 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>R$ 139.1</t>
+          <t>R$ 139,1</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -13281,7 +13281,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>0</v>
+        <v>139.1</v>
       </c>
       <c r="J220" s="1" t="n">
         <v>46075</v>
@@ -13299,7 +13299,7 @@
         <v>1001</v>
       </c>
       <c r="O220" t="n">
-        <v>0</v>
+        <v>2.575925925925926</v>
       </c>
     </row>
     <row r="221">
@@ -13399,7 +13399,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>305</v>
+        <v>305.73</v>
       </c>
       <c r="J222" s="1" t="n">
         <v>46075</v>
@@ -13417,7 +13417,7 @@
         <v>1001</v>
       </c>
       <c r="O222" t="n">
-        <v>2.798165137614679</v>
+        <v>2.804862385321101</v>
       </c>
     </row>
     <row r="223">
@@ -13458,7 +13458,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>121</v>
+        <v>121.79</v>
       </c>
       <c r="J223" s="1" t="n">
         <v>46075</v>
@@ -13476,7 +13476,7 @@
         <v>1001</v>
       </c>
       <c r="O223" t="n">
-        <v>2.160714285714286</v>
+        <v>2.174821428571429</v>
       </c>
     </row>
     <row r="224">
@@ -13517,7 +13517,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>236</v>
+        <v>236.35</v>
       </c>
       <c r="J224" s="1" t="n">
         <v>46075</v>
@@ -13535,7 +13535,7 @@
         <v>1001</v>
       </c>
       <c r="O224" t="n">
-        <v>2.052173913043478</v>
+        <v>2.055217391304348</v>
       </c>
     </row>
     <row r="225">
@@ -13576,7 +13576,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>701</v>
+        <v>701.89</v>
       </c>
       <c r="J225" s="1" t="n">
         <v>46076</v>
@@ -13594,7 +13594,7 @@
         <v>1002</v>
       </c>
       <c r="O225" t="n">
-        <v>33.38095238095238</v>
+        <v>33.42333333333333</v>
       </c>
     </row>
     <row r="226">
@@ -13635,7 +13635,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>1205</v>
+        <v>1205.38</v>
       </c>
       <c r="J226" s="1" t="n">
         <v>46076</v>
@@ -13653,7 +13653,7 @@
         <v>1002</v>
       </c>
       <c r="O226" t="n">
-        <v>28.02325581395349</v>
+        <v>28.03209302325581</v>
       </c>
     </row>
     <row r="227">
@@ -13694,7 +13694,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>556</v>
+        <v>556.5</v>
       </c>
       <c r="J227" s="1" t="n">
         <v>46076</v>
@@ -13712,7 +13712,7 @@
         <v>1002</v>
       </c>
       <c r="O227" t="n">
-        <v>24.17391304347826</v>
+        <v>24.19565217391304</v>
       </c>
     </row>
     <row r="228">
@@ -13753,7 +13753,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>2287</v>
+        <v>2287.74</v>
       </c>
       <c r="J228" s="1" t="n">
         <v>46076</v>
@@ -13771,7 +13771,7 @@
         <v>1002</v>
       </c>
       <c r="O228" t="n">
-        <v>38.11666666666667</v>
+        <v>38.129</v>
       </c>
     </row>
     <row r="229">
@@ -13812,7 +13812,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>313</v>
+        <v>313.57</v>
       </c>
       <c r="J229" s="1" t="n">
         <v>46077</v>
@@ -13830,7 +13830,7 @@
         <v>1001</v>
       </c>
       <c r="O229" t="n">
-        <v>2.675213675213675</v>
+        <v>2.68008547008547</v>
       </c>
     </row>
     <row r="230">
@@ -13871,7 +13871,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>192</v>
+        <v>192.12</v>
       </c>
       <c r="J230" s="1" t="n">
         <v>46077</v>
@@ -13889,7 +13889,7 @@
         <v>1001</v>
       </c>
       <c r="O230" t="n">
-        <v>2</v>
+        <v>2.00125</v>
       </c>
     </row>
     <row r="231">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>R$ 255.83</t>
+          <t>R$ 255,83</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
@@ -13930,7 +13930,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>0</v>
+        <v>255.83</v>
       </c>
       <c r="J231" s="1" t="n">
         <v>46077</v>
@@ -13948,7 +13948,7 @@
         <v>1001</v>
       </c>
       <c r="O231" t="n">
-        <v>0</v>
+        <v>2.692947368421053</v>
       </c>
     </row>
     <row r="232">
@@ -13975,7 +13975,7 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>R$ 122.79</t>
+          <t>R$ 122,79</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
@@ -13989,7 +13989,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>0</v>
+        <v>122.79</v>
       </c>
       <c r="J232" s="1" t="n">
         <v>46077</v>
@@ -14007,7 +14007,7 @@
         <v>1001</v>
       </c>
       <c r="O232" t="n">
-        <v>0</v>
+        <v>2.0465</v>
       </c>
     </row>
     <row r="233">
@@ -14044,7 +14044,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>161</v>
+        <v>161.02</v>
       </c>
       <c r="J233" s="1" t="n">
         <v>46077</v>
@@ -14062,7 +14062,7 @@
         <v>1001</v>
       </c>
       <c r="O233" t="n">
-        <v>3.285714285714286</v>
+        <v>3.286122448979592</v>
       </c>
     </row>
     <row r="234">
@@ -14103,7 +14103,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>511</v>
+        <v>511.6</v>
       </c>
       <c r="J234" s="1" t="n">
         <v>46078</v>
@@ -14121,7 +14121,7 @@
         <v>1002</v>
       </c>
       <c r="O234" t="n">
-        <v>20.44</v>
+        <v>20.464</v>
       </c>
     </row>
     <row r="235">
@@ -14162,7 +14162,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>816</v>
+        <v>816.53</v>
       </c>
       <c r="J235" s="1" t="n">
         <v>46078</v>
@@ -14180,7 +14180,7 @@
         <v>1002</v>
       </c>
       <c r="O235" t="n">
-        <v>19.90243902439024</v>
+        <v>19.91536585365854</v>
       </c>
     </row>
     <row r="236">
@@ -14221,7 +14221,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>808</v>
+        <v>808.66</v>
       </c>
       <c r="J236" s="1" t="n">
         <v>46078</v>
@@ -14239,7 +14239,7 @@
         <v>1002</v>
       </c>
       <c r="O236" t="n">
-        <v>14.96296296296296</v>
+        <v>14.97518518518518</v>
       </c>
     </row>
     <row r="237">
@@ -14280,7 +14280,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>1231</v>
+        <v>1231.37</v>
       </c>
       <c r="J237" s="1" t="n">
         <v>46078</v>
@@ -14298,7 +14298,7 @@
         <v>1002</v>
       </c>
       <c r="O237" t="n">
-        <v>22.38181818181818</v>
+        <v>22.38854545454545</v>
       </c>
     </row>
     <row r="238">
@@ -14339,7 +14339,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>128</v>
+        <v>128.59</v>
       </c>
       <c r="J238" s="1" t="n">
         <v>46079</v>
@@ -14357,7 +14357,7 @@
         <v>1001</v>
       </c>
       <c r="O238" t="n">
-        <v>2.169491525423729</v>
+        <v>2.179491525423729</v>
       </c>
     </row>
     <row r="239">
@@ -14384,7 +14384,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>R$ 293.01</t>
+          <t>R$ 293,01</t>
         </is>
       </c>
       <c r="G239" t="inlineStr"/>
@@ -14394,7 +14394,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>0</v>
+        <v>293.01</v>
       </c>
       <c r="J239" s="1" t="n">
         <v>46079</v>
@@ -14412,7 +14412,7 @@
         <v>1001</v>
       </c>
       <c r="O239" t="n">
-        <v>0</v>
+        <v>3.407093023255814</v>
       </c>
     </row>
     <row r="240">
@@ -14439,7 +14439,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>R$ 370.91</t>
+          <t>R$ 370,91</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
@@ -14453,7 +14453,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>0</v>
+        <v>370.91</v>
       </c>
       <c r="J240" s="1" t="n">
         <v>46079</v>
@@ -14471,7 +14471,7 @@
         <v>1001</v>
       </c>
       <c r="O240" t="n">
-        <v>0</v>
+        <v>3.1975</v>
       </c>
     </row>
     <row r="241">
@@ -14512,7 +14512,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>202</v>
+        <v>202.78</v>
       </c>
       <c r="J241" s="1" t="n">
         <v>46079</v>
@@ -14530,7 +14530,7 @@
         <v>1001</v>
       </c>
       <c r="O241" t="n">
-        <v>2.404761904761905</v>
+        <v>2.414047619047619</v>
       </c>
     </row>
     <row r="242">
@@ -14557,7 +14557,7 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>R$ 187.91</t>
+          <t>R$ 187,91</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
@@ -14571,7 +14571,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>0</v>
+        <v>187.91</v>
       </c>
       <c r="J242" s="1" t="n">
         <v>46079</v>
@@ -14589,7 +14589,7 @@
         <v>1001</v>
       </c>
       <c r="O242" t="n">
-        <v>0</v>
+        <v>3.184915254237288</v>
       </c>
     </row>
     <row r="243">
@@ -14630,7 +14630,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>539</v>
+        <v>539.4</v>
       </c>
       <c r="J243" s="1" t="n">
         <v>46080</v>
@@ -14648,7 +14648,7 @@
         <v>1002</v>
       </c>
       <c r="O243" t="n">
-        <v>19.96296296296296</v>
+        <v>19.97777777777778</v>
       </c>
     </row>
     <row r="244">
@@ -14689,7 +14689,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>1076</v>
+        <v>1076.88</v>
       </c>
       <c r="J244" s="1" t="n">
         <v>46080</v>
@@ -14707,7 +14707,7 @@
         <v>1002</v>
       </c>
       <c r="O244" t="n">
-        <v>21.52</v>
+        <v>21.5376</v>
       </c>
     </row>
     <row r="245">
@@ -14748,7 +14748,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>874</v>
+        <v>874.03</v>
       </c>
       <c r="J245" s="1" t="n">
         <v>46080</v>
@@ -14766,7 +14766,7 @@
         <v>1002</v>
       </c>
       <c r="O245" t="n">
-        <v>38</v>
+        <v>38.00130434782609</v>
       </c>
     </row>
     <row r="246">
@@ -14807,7 +14807,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>916</v>
+        <v>916.38</v>
       </c>
       <c r="J246" s="1" t="n">
         <v>46080</v>
@@ -14825,7 +14825,7 @@
         <v>1002</v>
       </c>
       <c r="O246" t="n">
-        <v>36.64</v>
+        <v>36.6552</v>
       </c>
     </row>
     <row r="247">
@@ -14852,7 +14852,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>R$ 378.96</t>
+          <t>R$ 378,96</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
@@ -14866,7 +14866,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>0</v>
+        <v>378.96</v>
       </c>
       <c r="J247" s="1" t="n">
         <v>46081</v>
@@ -14884,7 +14884,7 @@
         <v>1001</v>
       </c>
       <c r="O247" t="n">
-        <v>-0</v>
+        <v>-3.476697247706422</v>
       </c>
     </row>
     <row r="248">
@@ -14921,7 +14921,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>169</v>
+        <v>169.38</v>
       </c>
       <c r="J248" s="1" t="n">
         <v>46081</v>
@@ -14939,7 +14939,7 @@
         <v>1001</v>
       </c>
       <c r="O248" t="n">
-        <v>3.25</v>
+        <v>3.257307692307692</v>
       </c>
     </row>
     <row r="249">
@@ -14976,7 +14976,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>355</v>
+        <v>355.67</v>
       </c>
       <c r="J249" s="1" t="n">
         <v>46081</v>
@@ -14994,7 +14994,7 @@
         <v>1001</v>
       </c>
       <c r="O249" t="n">
-        <v>3.008474576271186</v>
+        <v>3.014152542372881</v>
       </c>
     </row>
     <row r="250">
@@ -15021,7 +15021,7 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>R$ 303.62</t>
+          <t>R$ 303,62</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
@@ -15035,7 +15035,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>0</v>
+        <v>303.62</v>
       </c>
       <c r="J250" s="1" t="n">
         <v>46081</v>
@@ -15053,7 +15053,7 @@
         <v>1001</v>
       </c>
       <c r="O250" t="n">
-        <v>0</v>
+        <v>2.976666666666667</v>
       </c>
     </row>
     <row r="251">
@@ -15080,7 +15080,7 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>R$ 289.02</t>
+          <t>R$ 289,02</t>
         </is>
       </c>
       <c r="G251" t="inlineStr"/>
@@ -15090,7 +15090,7 @@
         </is>
       </c>
       <c r="I251" t="n">
-        <v>0</v>
+        <v>289.02</v>
       </c>
       <c r="J251" s="1" t="n">
         <v>46081</v>
@@ -15108,7 +15108,7 @@
         <v>1001</v>
       </c>
       <c r="O251" t="n">
-        <v>0</v>
+        <v>2.603783783783784</v>
       </c>
     </row>
     <row r="252">
@@ -15135,7 +15135,7 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>R$ 87.3</t>
+          <t>R$ 87,3</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
@@ -15149,7 +15149,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>0</v>
+        <v>87.3</v>
       </c>
       <c r="J252" s="1" t="n">
         <v>46083</v>
@@ -15167,7 +15167,7 @@
         <v>1001</v>
       </c>
       <c r="O252" t="n">
-        <v>0</v>
+        <v>2.078571428571428</v>
       </c>
     </row>
     <row r="253">
@@ -15208,7 +15208,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>296</v>
+        <v>296.82</v>
       </c>
       <c r="J253" s="1" t="n">
         <v>46083</v>
@@ -15226,7 +15226,7 @@
         <v>1001</v>
       </c>
       <c r="O253" t="n">
-        <v>2.96</v>
+        <v>2.9682</v>
       </c>
     </row>
     <row r="254">
@@ -15263,7 +15263,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>127</v>
+        <v>127.13</v>
       </c>
       <c r="J254" s="1" t="n">
         <v>46083</v>
@@ -15281,7 +15281,7 @@
         <v>1001</v>
       </c>
       <c r="O254" t="n">
-        <v>2.309090909090909</v>
+        <v>2.311454545454545</v>
       </c>
     </row>
     <row r="255">
@@ -15308,7 +15308,7 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>R$ 114.44</t>
+          <t>R$ 114,44</t>
         </is>
       </c>
       <c r="G255" t="inlineStr"/>
@@ -15318,7 +15318,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>0</v>
+        <v>114.44</v>
       </c>
       <c r="J255" s="1" t="n">
         <v>46083</v>
@@ -15336,7 +15336,7 @@
         <v>1001</v>
       </c>
       <c r="O255" t="n">
-        <v>0</v>
+        <v>2.791219512195122</v>
       </c>
     </row>
     <row r="256">
@@ -15377,7 +15377,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>137</v>
+        <v>137.33</v>
       </c>
       <c r="J256" s="1" t="n">
         <v>46083</v>
@@ -15395,7 +15395,7 @@
         <v>1001</v>
       </c>
       <c r="O256" t="n">
-        <v>2.446428571428572</v>
+        <v>2.452321428571429</v>
       </c>
     </row>
     <row r="257">
@@ -15436,7 +15436,7 @@
         </is>
       </c>
       <c r="I257" t="n">
-        <v>1653</v>
+        <v>1653.04</v>
       </c>
       <c r="J257" s="1" t="n">
         <v>46083</v>
@@ -15454,7 +15454,7 @@
         <v>1002</v>
       </c>
       <c r="O257" t="n">
-        <v>35.17021276595744</v>
+        <v>35.17106382978724</v>
       </c>
     </row>
     <row r="258">
@@ -15495,7 +15495,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>493</v>
+        <v>493.26</v>
       </c>
       <c r="J258" s="1" t="n">
         <v>46083</v>
@@ -15513,7 +15513,7 @@
         <v>1002</v>
       </c>
       <c r="O258" t="n">
-        <v>15.40625</v>
+        <v>15.414375</v>
       </c>
     </row>
     <row r="259">
@@ -15554,7 +15554,7 @@
         </is>
       </c>
       <c r="I259" t="n">
-        <v>970</v>
+        <v>970.67</v>
       </c>
       <c r="J259" s="1" t="n">
         <v>46083</v>
@@ -15572,7 +15572,7 @@
         <v>1002</v>
       </c>
       <c r="O259" t="n">
-        <v>29.39393939393939</v>
+        <v>29.41424242424242</v>
       </c>
     </row>
     <row r="260">
@@ -15613,7 +15613,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>1218</v>
+        <v>1218.64</v>
       </c>
       <c r="J260" s="1" t="n">
         <v>46083</v>
@@ -15631,7 +15631,7 @@
         <v>1002</v>
       </c>
       <c r="O260" t="n">
-        <v>33.83333333333334</v>
+        <v>33.85111111111112</v>
       </c>
     </row>
     <row r="261">
@@ -15672,7 +15672,7 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>264</v>
+        <v>264.22</v>
       </c>
       <c r="J261" s="1" t="n">
         <v>46085</v>
@@ -15690,7 +15690,7 @@
         <v>1001</v>
       </c>
       <c r="O261" t="n">
-        <v>2.4</v>
+        <v>2.402</v>
       </c>
     </row>
     <row r="262">
@@ -15717,7 +15717,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>R$ 183.58</t>
+          <t>R$ 183,58</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
@@ -15731,7 +15731,7 @@
         </is>
       </c>
       <c r="I262" t="n">
-        <v>0</v>
+        <v>183.58</v>
       </c>
       <c r="J262" s="1" t="n">
         <v>46085</v>
@@ -15749,7 +15749,7 @@
         <v>1001</v>
       </c>
       <c r="O262" t="n">
-        <v>0</v>
+        <v>2.699705882352941</v>
       </c>
     </row>
     <row r="263">
@@ -15786,7 +15786,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>185</v>
+        <v>185.86</v>
       </c>
       <c r="J263" s="1" t="n">
         <v>46085</v>
@@ -15804,7 +15804,7 @@
         <v>1001</v>
       </c>
       <c r="O263" t="n">
-        <v>2.402597402597403</v>
+        <v>2.413766233766234</v>
       </c>
     </row>
     <row r="264">
@@ -15845,7 +15845,7 @@
         </is>
       </c>
       <c r="I264" t="n">
-        <v>132</v>
+        <v>132.8</v>
       </c>
       <c r="J264" s="1" t="n">
         <v>46085</v>
@@ -15863,7 +15863,7 @@
         <v>1001</v>
       </c>
       <c r="O264" t="n">
-        <v>2.75</v>
+        <v>2.766666666666667</v>
       </c>
     </row>
     <row r="265">
@@ -15904,7 +15904,7 @@
         </is>
       </c>
       <c r="I265" t="n">
-        <v>168</v>
+        <v>168.22</v>
       </c>
       <c r="J265" s="1" t="n">
         <v>46085</v>
@@ -15922,7 +15922,7 @@
         <v>1001</v>
       </c>
       <c r="O265" t="n">
-        <v>3.054545454545455</v>
+        <v>3.058545454545455</v>
       </c>
     </row>
     <row r="266">
@@ -15963,7 +15963,7 @@
         </is>
       </c>
       <c r="I266" t="n">
-        <v>1394</v>
+        <v>1394.7</v>
       </c>
       <c r="J266" s="1" t="n">
         <v>46085</v>
@@ -15981,7 +15981,7 @@
         <v>1002</v>
       </c>
       <c r="O266" t="n">
-        <v>34.85</v>
+        <v>34.8675</v>
       </c>
     </row>
     <row r="267">
@@ -16022,7 +16022,7 @@
         </is>
       </c>
       <c r="I267" t="n">
-        <v>1064</v>
+        <v>1064.95</v>
       </c>
       <c r="J267" s="1" t="n">
         <v>46085</v>
@@ -16040,7 +16040,7 @@
         <v>1002</v>
       </c>
       <c r="O267" t="n">
-        <v>29.55555555555556</v>
+        <v>29.58194444444445</v>
       </c>
     </row>
     <row r="268">
@@ -16081,7 +16081,7 @@
         </is>
       </c>
       <c r="I268" t="n">
-        <v>1428</v>
+        <v>1428.05</v>
       </c>
       <c r="J268" s="1" t="n">
         <v>46085</v>
@@ -16099,7 +16099,7 @@
         <v>1002</v>
       </c>
       <c r="O268" t="n">
-        <v>37.57894736842105</v>
+        <v>37.58026315789473</v>
       </c>
     </row>
     <row r="269">
@@ -16140,7 +16140,7 @@
         </is>
       </c>
       <c r="I269" t="n">
-        <v>1025</v>
+        <v>1025.9</v>
       </c>
       <c r="J269" s="1" t="n">
         <v>46085</v>
@@ -16158,7 +16158,7 @@
         <v>1002</v>
       </c>
       <c r="O269" t="n">
-        <v>20.5</v>
+        <v>20.518</v>
       </c>
     </row>
     <row r="270">
@@ -16199,7 +16199,7 @@
         </is>
       </c>
       <c r="I270" t="n">
-        <v>285</v>
+        <v>285.61</v>
       </c>
       <c r="J270" s="1" t="n">
         <v>46087</v>
@@ -16217,7 +16217,7 @@
         <v>1001</v>
       </c>
       <c r="O270" t="n">
-        <v>2.590909090909091</v>
+        <v>2.596454545454546</v>
       </c>
     </row>
     <row r="271">
@@ -16258,7 +16258,7 @@
         </is>
       </c>
       <c r="I271" t="n">
-        <v>361</v>
+        <v>361.2</v>
       </c>
       <c r="J271" s="1" t="n">
         <v>46087</v>
@@ -16276,7 +16276,7 @@
         <v>1001</v>
       </c>
       <c r="O271" t="n">
-        <v>3.033613445378151</v>
+        <v>3.035294117647059</v>
       </c>
     </row>
     <row r="272">
@@ -16317,7 +16317,7 @@
         </is>
       </c>
       <c r="I272" t="n">
-        <v>97</v>
+        <v>97.03</v>
       </c>
       <c r="J272" s="1" t="n">
         <v>46087</v>
@@ -16335,7 +16335,7 @@
         <v>1001</v>
       </c>
       <c r="O272" t="n">
-        <v>2.063829787234043</v>
+        <v>2.064468085106383</v>
       </c>
     </row>
     <row r="273">
@@ -16376,7 +16376,7 @@
         </is>
       </c>
       <c r="I273" t="n">
-        <v>121</v>
+        <v>121.38</v>
       </c>
       <c r="J273" s="1" t="n">
         <v>46087</v>
@@ -16394,7 +16394,7 @@
         <v>1001</v>
       </c>
       <c r="O273" t="n">
-        <v>2.880952380952381</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="274">
@@ -16421,7 +16421,7 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>R$ 178.04</t>
+          <t>R$ 178,04</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
@@ -16435,7 +16435,7 @@
         </is>
       </c>
       <c r="I274" t="n">
-        <v>0</v>
+        <v>178.04</v>
       </c>
       <c r="J274" s="1" t="n">
         <v>46087</v>
@@ -16453,7 +16453,7 @@
         <v>1001</v>
       </c>
       <c r="O274" t="n">
-        <v>0</v>
+        <v>2.739076923076923</v>
       </c>
     </row>
     <row r="275">
@@ -16494,7 +16494,7 @@
         </is>
       </c>
       <c r="I275" t="n">
-        <v>404</v>
+        <v>404.46</v>
       </c>
       <c r="J275" s="1" t="n">
         <v>46087</v>
@@ -16512,7 +16512,7 @@
         <v>1002</v>
       </c>
       <c r="O275" t="n">
-        <v>18.36363636363636</v>
+        <v>18.38454545454545</v>
       </c>
     </row>
     <row r="276">
@@ -16553,7 +16553,7 @@
         </is>
       </c>
       <c r="I276" t="n">
-        <v>1523</v>
+        <v>1523.26</v>
       </c>
       <c r="J276" s="1" t="n">
         <v>46087</v>
@@ -16571,7 +16571,7 @@
         <v>1002</v>
       </c>
       <c r="O276" t="n">
-        <v>31.72916666666667</v>
+        <v>31.73458333333333</v>
       </c>
     </row>
     <row r="277">
@@ -16612,7 +16612,7 @@
         </is>
       </c>
       <c r="I277" t="n">
-        <v>1622</v>
+        <v>1622.06</v>
       </c>
       <c r="J277" s="1" t="n">
         <v>46087</v>
@@ -16630,7 +16630,7 @@
         <v>1002</v>
       </c>
       <c r="O277" t="n">
-        <v>36.04444444444444</v>
+        <v>36.04577777777778</v>
       </c>
     </row>
     <row r="278">
@@ -16671,7 +16671,7 @@
         </is>
       </c>
       <c r="I278" t="n">
-        <v>874</v>
+        <v>874.53</v>
       </c>
       <c r="J278" s="1" t="n">
         <v>46087</v>
@@ -16689,7 +16689,7 @@
         <v>1002</v>
       </c>
       <c r="O278" t="n">
-        <v>19.42222222222222</v>
+        <v>19.434</v>
       </c>
     </row>
     <row r="279">
@@ -16716,7 +16716,7 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>R$ 94.42</t>
+          <t>R$ 94,42</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
@@ -16730,7 +16730,7 @@
         </is>
       </c>
       <c r="I279" t="n">
-        <v>0</v>
+        <v>94.42</v>
       </c>
       <c r="J279" s="1" t="n">
         <v>46089</v>
@@ -16748,7 +16748,7 @@
         <v>1001</v>
       </c>
       <c r="O279" t="n">
-        <v>0</v>
+        <v>2.3605</v>
       </c>
     </row>
     <row r="280">
@@ -16789,7 +16789,7 @@
         </is>
       </c>
       <c r="I280" t="n">
-        <v>80</v>
+        <v>80.42</v>
       </c>
       <c r="J280" s="1" t="n">
         <v>46089</v>
@@ -16807,7 +16807,7 @@
         <v>1001</v>
       </c>
       <c r="O280" t="n">
-        <v>2</v>
+        <v>2.0105</v>
       </c>
     </row>
     <row r="281">
@@ -16834,7 +16834,7 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>R$ 127.8</t>
+          <t>R$ 127,8</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
@@ -16848,7 +16848,7 @@
         </is>
       </c>
       <c r="I281" t="n">
-        <v>0</v>
+        <v>127.8</v>
       </c>
       <c r="J281" s="1" t="n">
         <v>46089</v>
@@ -16866,7 +16866,7 @@
         <v>1001</v>
       </c>
       <c r="O281" t="n">
-        <v>0</v>
+        <v>2.505882352941176</v>
       </c>
     </row>
     <row r="282">
@@ -16907,7 +16907,7 @@
         </is>
       </c>
       <c r="I282" t="n">
-        <v>248</v>
+        <v>248.32</v>
       </c>
       <c r="J282" s="1" t="n">
         <v>46089</v>
@@ -16925,7 +16925,7 @@
         <v>1001</v>
       </c>
       <c r="O282" t="n">
-        <v>3.492957746478873</v>
+        <v>3.497464788732394</v>
       </c>
     </row>
     <row r="283">
@@ -16966,7 +16966,7 @@
         </is>
       </c>
       <c r="I283" t="n">
-        <v>167</v>
+        <v>167.96</v>
       </c>
       <c r="J283" s="1" t="n">
         <v>46089</v>
@@ -16984,7 +16984,7 @@
         <v>1001</v>
       </c>
       <c r="O283" t="n">
-        <v>3.274509803921569</v>
+        <v>3.293333333333333</v>
       </c>
     </row>
     <row r="284">
@@ -17025,7 +17025,7 @@
         </is>
       </c>
       <c r="I284" t="n">
-        <v>1494</v>
+        <v>1494.09</v>
       </c>
       <c r="J284" s="1" t="n">
         <v>46090</v>
@@ -17043,7 +17043,7 @@
         <v>1002</v>
       </c>
       <c r="O284" t="n">
-        <v>29.29411764705882</v>
+        <v>29.29588235294117</v>
       </c>
     </row>
     <row r="285">
@@ -17084,7 +17084,7 @@
         </is>
       </c>
       <c r="I285" t="n">
-        <v>958</v>
+        <v>958.83</v>
       </c>
       <c r="J285" s="1" t="n">
         <v>46090</v>
@@ -17102,7 +17102,7 @@
         <v>1002</v>
       </c>
       <c r="O285" t="n">
-        <v>29.03030303030303</v>
+        <v>29.05545454545455</v>
       </c>
     </row>
     <row r="286">
@@ -17143,7 +17143,7 @@
         </is>
       </c>
       <c r="I286" t="n">
-        <v>585</v>
+        <v>585.9</v>
       </c>
       <c r="J286" s="1" t="n">
         <v>46090</v>
@@ -17161,7 +17161,7 @@
         <v>1002</v>
       </c>
       <c r="O286" t="n">
-        <v>18.28125</v>
+        <v>18.309375</v>
       </c>
     </row>
     <row r="287">
@@ -17202,7 +17202,7 @@
         </is>
       </c>
       <c r="I287" t="n">
-        <v>1605</v>
+        <v>1605.25</v>
       </c>
       <c r="J287" s="1" t="n">
         <v>46090</v>
@@ -17220,7 +17220,7 @@
         <v>1002</v>
       </c>
       <c r="O287" t="n">
-        <v>31.47058823529412</v>
+        <v>31.47549019607843</v>
       </c>
     </row>
     <row r="288">
@@ -17261,7 +17261,7 @@
         </is>
       </c>
       <c r="I288" t="n">
-        <v>121</v>
+        <v>121.17</v>
       </c>
       <c r="J288" s="1" t="n">
         <v>46091</v>
@@ -17279,7 +17279,7 @@
         <v>1001</v>
       </c>
       <c r="O288" t="n">
-        <v>2.2</v>
+        <v>2.203090909090909</v>
       </c>
     </row>
     <row r="289">
@@ -17320,7 +17320,7 @@
         </is>
       </c>
       <c r="I289" t="n">
-        <v>317</v>
+        <v>317.08</v>
       </c>
       <c r="J289" s="1" t="n">
         <v>46091</v>
@@ -17338,7 +17338,7 @@
         <v>1001</v>
       </c>
       <c r="O289" t="n">
-        <v>2.732758620689655</v>
+        <v>2.733448275862069</v>
       </c>
     </row>
     <row r="290">
@@ -17379,7 +17379,7 @@
         </is>
       </c>
       <c r="I290" t="n">
-        <v>205</v>
+        <v>205.1</v>
       </c>
       <c r="J290" s="1" t="n">
         <v>46091</v>
@@ -17397,7 +17397,7 @@
         <v>1001</v>
       </c>
       <c r="O290" t="n">
-        <v>2.469879518072289</v>
+        <v>2.471084337349398</v>
       </c>
     </row>
     <row r="291">
@@ -17424,7 +17424,7 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>R$ 260.72</t>
+          <t>R$ 260,72</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
@@ -17438,7 +17438,7 @@
         </is>
       </c>
       <c r="I291" t="n">
-        <v>0</v>
+        <v>260.72</v>
       </c>
       <c r="J291" s="1" t="n">
         <v>46091</v>
@@ -17456,7 +17456,7 @@
         <v>1001</v>
       </c>
       <c r="O291" t="n">
-        <v>0</v>
+        <v>3.179512195121951</v>
       </c>
     </row>
     <row r="292">
@@ -17483,7 +17483,7 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>R$ 351.95</t>
+          <t>R$ 351,95</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
@@ -17497,7 +17497,7 @@
         </is>
       </c>
       <c r="I292" t="n">
-        <v>0</v>
+        <v>351.95</v>
       </c>
       <c r="J292" s="1" t="n">
         <v>46091</v>
@@ -17515,7 +17515,7 @@
         <v>1001</v>
       </c>
       <c r="O292" t="n">
-        <v>0</v>
+        <v>3.087280701754386</v>
       </c>
     </row>
     <row r="293">
@@ -17556,7 +17556,7 @@
         </is>
       </c>
       <c r="I293" t="n">
-        <v>694</v>
+        <v>694.61</v>
       </c>
       <c r="J293" s="1" t="n">
         <v>46092</v>
@@ -17574,7 +17574,7 @@
         <v>1002</v>
       </c>
       <c r="O293" t="n">
-        <v>23.13333333333333</v>
+        <v>23.15366666666667</v>
       </c>
     </row>
     <row r="294">
@@ -17615,7 +17615,7 @@
         </is>
       </c>
       <c r="I294" t="n">
-        <v>1566</v>
+        <v>1566.52</v>
       </c>
       <c r="J294" s="1" t="n">
         <v>46092</v>
@@ -17633,7 +17633,7 @@
         <v>1002</v>
       </c>
       <c r="O294" t="n">
-        <v>34.8</v>
+        <v>34.81155555555556</v>
       </c>
     </row>
     <row r="295">
@@ -17674,7 +17674,7 @@
         </is>
       </c>
       <c r="I295" t="n">
-        <v>765</v>
+        <v>765.58</v>
       </c>
       <c r="J295" s="1" t="n">
         <v>46092</v>
@@ -17692,7 +17692,7 @@
         <v>1002</v>
       </c>
       <c r="O295" t="n">
-        <v>13.66071428571429</v>
+        <v>13.67107142857143</v>
       </c>
     </row>
     <row r="296">
@@ -17733,7 +17733,7 @@
         </is>
       </c>
       <c r="I296" t="n">
-        <v>544</v>
+        <v>544.84</v>
       </c>
       <c r="J296" s="1" t="n">
         <v>46092</v>
@@ -17751,7 +17751,7 @@
         <v>1002</v>
       </c>
       <c r="O296" t="n">
-        <v>27.2</v>
+        <v>27.242</v>
       </c>
     </row>
     <row r="297">
@@ -17778,7 +17778,7 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>R$ 144.03</t>
+          <t>R$ 144,03</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
@@ -17792,7 +17792,7 @@
         </is>
       </c>
       <c r="I297" t="n">
-        <v>0</v>
+        <v>144.03</v>
       </c>
       <c r="J297" s="1" t="n">
         <v>46093</v>
@@ -17810,7 +17810,7 @@
         <v>1001</v>
       </c>
       <c r="O297" t="n">
-        <v>0</v>
+        <v>2.441186440677966</v>
       </c>
     </row>
     <row r="298">
@@ -17851,7 +17851,7 @@
         </is>
       </c>
       <c r="I298" t="n">
-        <v>328</v>
+        <v>328.53</v>
       </c>
       <c r="J298" s="1" t="n">
         <v>46093</v>
@@ -17869,7 +17869,7 @@
         <v>1001</v>
       </c>
       <c r="O298" t="n">
-        <v>3.313131313131313</v>
+        <v>3.318484848484848</v>
       </c>
     </row>
     <row r="299">
@@ -17910,7 +17910,7 @@
         </is>
       </c>
       <c r="I299" t="n">
-        <v>133</v>
+        <v>133.69</v>
       </c>
       <c r="J299" s="1" t="n">
         <v>46093</v>
@@ -17928,7 +17928,7 @@
         <v>1001</v>
       </c>
       <c r="O299" t="n">
-        <v>2.955555555555556</v>
+        <v>2.970888888888889</v>
       </c>
     </row>
     <row r="300">
@@ -17969,7 +17969,7 @@
         </is>
       </c>
       <c r="I300" t="n">
-        <v>274</v>
+        <v>274.08</v>
       </c>
       <c r="J300" s="1" t="n">
         <v>46093</v>
@@ -17987,7 +17987,7 @@
         <v>1001</v>
       </c>
       <c r="O300" t="n">
-        <v>2.468468468468469</v>
+        <v>2.469189189189189</v>
       </c>
     </row>
     <row r="301">
@@ -18028,7 +18028,7 @@
         </is>
       </c>
       <c r="I301" t="n">
-        <v>117</v>
+        <v>117.38</v>
       </c>
       <c r="J301" s="1" t="n">
         <v>46093</v>
@@ -18046,7 +18046,7 @@
         <v>1001</v>
       </c>
       <c r="O301" t="n">
-        <v>2.207547169811321</v>
+        <v>2.214716981132075</v>
       </c>
     </row>
     <row r="302">
@@ -18087,7 +18087,7 @@
         </is>
       </c>
       <c r="I302" t="n">
-        <v>1536</v>
+        <v>1536.61</v>
       </c>
       <c r="J302" s="1" t="n">
         <v>46094</v>
@@ -18105,7 +18105,7 @@
         <v>1002</v>
       </c>
       <c r="O302" t="n">
-        <v>32.68085106382978</v>
+        <v>32.69382978723404</v>
       </c>
     </row>
     <row r="303">
@@ -18146,7 +18146,7 @@
         </is>
       </c>
       <c r="I303" t="n">
-        <v>2035</v>
+        <v>2035.59</v>
       </c>
       <c r="J303" s="1" t="n">
         <v>46094</v>
@@ -18164,7 +18164,7 @@
         <v>1002</v>
       </c>
       <c r="O303" t="n">
-        <v>38.39622641509434</v>
+        <v>38.40735849056604</v>
       </c>
     </row>
     <row r="304">
@@ -18205,7 +18205,7 @@
         </is>
       </c>
       <c r="I304" t="n">
-        <v>1429</v>
+        <v>1429.43</v>
       </c>
       <c r="J304" s="1" t="n">
         <v>46094</v>
@@ -18223,7 +18223,7 @@
         <v>1002</v>
       </c>
       <c r="O304" t="n">
-        <v>31.75555555555556</v>
+        <v>31.76511111111111</v>
       </c>
     </row>
     <row r="305">
@@ -18264,7 +18264,7 @@
         </is>
       </c>
       <c r="I305" t="n">
-        <v>821</v>
+        <v>821.1900000000001</v>
       </c>
       <c r="J305" s="1" t="n">
         <v>46094</v>
@@ -18282,7 +18282,7 @@
         <v>1002</v>
       </c>
       <c r="O305" t="n">
-        <v>31.57692307692308</v>
+        <v>31.58423076923077</v>
       </c>
     </row>
     <row r="306">
@@ -18323,7 +18323,7 @@
         </is>
       </c>
       <c r="I306" t="n">
-        <v>335</v>
+        <v>335.15</v>
       </c>
       <c r="J306" s="1" t="n">
         <v>46095</v>
@@ -18341,7 +18341,7 @@
         <v>1001</v>
       </c>
       <c r="O306" t="n">
-        <v>2.791666666666667</v>
+        <v>2.792916666666666</v>
       </c>
     </row>
     <row r="307">
@@ -18378,7 +18378,7 @@
         </is>
       </c>
       <c r="I307" t="n">
-        <v>98</v>
+        <v>98.65000000000001</v>
       </c>
       <c r="J307" s="1" t="n">
         <v>46095</v>
@@ -18396,7 +18396,7 @@
         <v>1001</v>
       </c>
       <c r="O307" t="n">
-        <v>-2.177777777777778</v>
+        <v>-2.192222222222223</v>
       </c>
     </row>
     <row r="308">
@@ -18423,7 +18423,7 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>R$ 262.99</t>
+          <t>R$ 262,99</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
@@ -18437,7 +18437,7 @@
         </is>
       </c>
       <c r="I308" t="n">
-        <v>0</v>
+        <v>262.99</v>
       </c>
       <c r="J308" s="1" t="n">
         <v>46095</v>
@@ -18455,7 +18455,7 @@
         <v>1001</v>
       </c>
       <c r="O308" t="n">
-        <v>0</v>
+        <v>2.306929824561403</v>
       </c>
     </row>
     <row r="309">
@@ -18492,7 +18492,7 @@
         </is>
       </c>
       <c r="I309" t="n">
-        <v>184</v>
+        <v>184.59</v>
       </c>
       <c r="J309" s="1" t="n">
         <v>46095</v>
@@ -18510,7 +18510,7 @@
         <v>1001</v>
       </c>
       <c r="O309" t="n">
-        <v>2.044444444444444</v>
+        <v>2.051</v>
       </c>
     </row>
     <row r="310">
@@ -18547,7 +18547,7 @@
         </is>
       </c>
       <c r="I310" t="n">
-        <v>298</v>
+        <v>298.53</v>
       </c>
       <c r="J310" s="1" t="n">
         <v>46095</v>
@@ -18565,7 +18565,7 @@
         <v>1001</v>
       </c>
       <c r="O310" t="n">
-        <v>3.465116279069767</v>
+        <v>3.471279069767442</v>
       </c>
     </row>
     <row r="311">
@@ -18602,7 +18602,7 @@
         </is>
       </c>
       <c r="I311" t="n">
-        <v>344</v>
+        <v>344.52</v>
       </c>
       <c r="J311" s="1" t="n">
         <v>46097</v>
@@ -18620,7 +18620,7 @@
         <v>1001</v>
       </c>
       <c r="O311" t="n">
-        <v>3.372549019607843</v>
+        <v>3.377647058823529</v>
       </c>
     </row>
     <row r="312">
@@ -18661,7 +18661,7 @@
         </is>
       </c>
       <c r="I312" t="n">
-        <v>132</v>
+        <v>132.28</v>
       </c>
       <c r="J312" s="1" t="n">
         <v>46097</v>
@@ -18679,7 +18679,7 @@
         <v>1001</v>
       </c>
       <c r="O312" t="n">
-        <v>2.4</v>
+        <v>2.405090909090909</v>
       </c>
     </row>
     <row r="313">
@@ -18720,7 +18720,7 @@
         </is>
       </c>
       <c r="I313" t="n">
-        <v>268</v>
+        <v>268.93</v>
       </c>
       <c r="J313" s="1" t="n">
         <v>46097</v>
@@ -18738,7 +18738,7 @@
         <v>1001</v>
       </c>
       <c r="O313" t="n">
-        <v>2.881720430107527</v>
+        <v>2.891720430107527</v>
       </c>
     </row>
     <row r="314">
@@ -18765,7 +18765,7 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>R$ 97.72</t>
+          <t>R$ 97,72</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
@@ -18779,7 +18779,7 @@
         </is>
       </c>
       <c r="I314" t="n">
-        <v>0</v>
+        <v>97.72</v>
       </c>
       <c r="J314" s="1" t="n">
         <v>46097</v>
@@ -18797,7 +18797,7 @@
         <v>1001</v>
       </c>
       <c r="O314" t="n">
-        <v>0</v>
+        <v>2.326666666666667</v>
       </c>
     </row>
     <row r="315">
@@ -18824,7 +18824,7 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>R$ 303.15</t>
+          <t>R$ 303,15</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
@@ -18838,7 +18838,7 @@
         </is>
       </c>
       <c r="I315" t="n">
-        <v>0</v>
+        <v>303.15</v>
       </c>
       <c r="J315" s="1" t="n">
         <v>46097</v>
@@ -18856,7 +18856,7 @@
         <v>1001</v>
       </c>
       <c r="O315" t="n">
-        <v>0</v>
+        <v>2.52625</v>
       </c>
     </row>
     <row r="316">
@@ -18897,7 +18897,7 @@
         </is>
       </c>
       <c r="I316" t="n">
-        <v>458</v>
+        <v>458.66</v>
       </c>
       <c r="J316" s="1" t="n">
         <v>46097</v>
@@ -18915,7 +18915,7 @@
         <v>1002</v>
       </c>
       <c r="O316" t="n">
-        <v>22.9</v>
+        <v>22.933</v>
       </c>
     </row>
     <row r="317">
@@ -18956,7 +18956,7 @@
         </is>
       </c>
       <c r="I317" t="n">
-        <v>1012</v>
+        <v>1012.25</v>
       </c>
       <c r="J317" s="1" t="n">
         <v>46097</v>
@@ -18974,7 +18974,7 @@
         <v>1002</v>
       </c>
       <c r="O317" t="n">
-        <v>27.35135135135135</v>
+        <v>27.35810810810811</v>
       </c>
     </row>
     <row r="318">
@@ -19015,7 +19015,7 @@
         </is>
       </c>
       <c r="I318" t="n">
-        <v>939</v>
+        <v>939.84</v>
       </c>
       <c r="J318" s="1" t="n">
         <v>46097</v>
@@ -19033,7 +19033,7 @@
         <v>1002</v>
       </c>
       <c r="O318" t="n">
-        <v>34.77777777777778</v>
+        <v>34.80888888888889</v>
       </c>
     </row>
     <row r="319">
@@ -19074,7 +19074,7 @@
         </is>
       </c>
       <c r="I319" t="n">
-        <v>764</v>
+        <v>764.63</v>
       </c>
       <c r="J319" s="1" t="n">
         <v>46097</v>
@@ -19092,7 +19092,7 @@
         <v>1002</v>
       </c>
       <c r="O319" t="n">
-        <v>28.2962962962963</v>
+        <v>28.31962962962963</v>
       </c>
     </row>
     <row r="320">
@@ -19133,7 +19133,7 @@
         </is>
       </c>
       <c r="I320" t="n">
-        <v>197</v>
+        <v>197.98</v>
       </c>
       <c r="J320" s="1" t="n">
         <v>46099</v>
@@ -19151,7 +19151,7 @@
         <v>1001</v>
       </c>
       <c r="O320" t="n">
-        <v>2.940298507462686</v>
+        <v>2.954925373134328</v>
       </c>
     </row>
     <row r="321">
@@ -19192,7 +19192,7 @@
         </is>
       </c>
       <c r="I321" t="n">
-        <v>122</v>
+        <v>122.17</v>
       </c>
       <c r="J321" s="1" t="n">
         <v>46099</v>
@@ -19210,7 +19210,7 @@
         <v>1001</v>
       </c>
       <c r="O321" t="n">
-        <v>2.259259259259259</v>
+        <v>2.262407407407407</v>
       </c>
     </row>
     <row r="322">
@@ -19251,7 +19251,7 @@
         </is>
       </c>
       <c r="I322" t="n">
-        <v>299</v>
+        <v>299.94</v>
       </c>
       <c r="J322" s="1" t="n">
         <v>46099</v>
@@ -19269,7 +19269,7 @@
         <v>1001</v>
       </c>
       <c r="O322" t="n">
-        <v>3.397727272727273</v>
+        <v>3.408409090909091</v>
       </c>
     </row>
     <row r="323">
@@ -19296,7 +19296,7 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>R$ 110.58</t>
+          <t>R$ 110,58</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
@@ -19310,7 +19310,7 @@
         </is>
       </c>
       <c r="I323" t="n">
-        <v>0</v>
+        <v>110.58</v>
       </c>
       <c r="J323" s="1" t="n">
         <v>46099</v>
@@ -19328,7 +19328,7 @@
         <v>1001</v>
       </c>
       <c r="O323" t="n">
-        <v>0</v>
+        <v>2.457333333333333</v>
       </c>
     </row>
     <row r="324">
@@ -19369,7 +19369,7 @@
         </is>
       </c>
       <c r="I324" t="n">
-        <v>236</v>
+        <v>236.22</v>
       </c>
       <c r="J324" s="1" t="n">
         <v>46099</v>
@@ -19387,7 +19387,7 @@
         <v>1001</v>
       </c>
       <c r="O324" t="n">
-        <v>2.226415094339623</v>
+        <v>2.228490566037736</v>
       </c>
     </row>
     <row r="325">
@@ -19428,7 +19428,7 @@
         </is>
       </c>
       <c r="I325" t="n">
-        <v>1314</v>
+        <v>1314.69</v>
       </c>
       <c r="J325" s="1" t="n">
         <v>46099</v>
@@ -19446,7 +19446,7 @@
         <v>1002</v>
       </c>
       <c r="O325" t="n">
-        <v>35.51351351351352</v>
+        <v>35.53216216216217</v>
       </c>
     </row>
     <row r="326">
@@ -19487,7 +19487,7 @@
         </is>
       </c>
       <c r="I326" t="n">
-        <v>2055</v>
+        <v>2055.19</v>
       </c>
       <c r="J326" s="1" t="n">
         <v>46099</v>
@@ -19505,7 +19505,7 @@
         <v>1002</v>
       </c>
       <c r="O326" t="n">
-        <v>34.83050847457627</v>
+        <v>34.83372881355933</v>
       </c>
     </row>
     <row r="327">
@@ -19546,7 +19546,7 @@
         </is>
       </c>
       <c r="I327" t="n">
-        <v>775</v>
+        <v>775.63</v>
       </c>
       <c r="J327" s="1" t="n">
         <v>46099</v>
@@ -19564,7 +19564,7 @@
         <v>1002</v>
       </c>
       <c r="O327" t="n">
-        <v>19.87179487179487</v>
+        <v>19.88794871794872</v>
       </c>
     </row>
     <row r="328">
@@ -19605,7 +19605,7 @@
         </is>
       </c>
       <c r="I328" t="n">
-        <v>1072</v>
+        <v>1072.33</v>
       </c>
       <c r="J328" s="1" t="n">
         <v>46099</v>
@@ -19623,7 +19623,7 @@
         <v>1002</v>
       </c>
       <c r="O328" t="n">
-        <v>23.82222222222222</v>
+        <v>23.82955555555555</v>
       </c>
     </row>
     <row r="329">
@@ -19664,7 +19664,7 @@
         </is>
       </c>
       <c r="I329" t="n">
-        <v>157</v>
+        <v>157.41</v>
       </c>
       <c r="J329" s="1" t="n">
         <v>46101</v>
@@ -19682,7 +19682,7 @@
         <v>1001</v>
       </c>
       <c r="O329" t="n">
-        <v>3.07843137254902</v>
+        <v>3.086470588235294</v>
       </c>
     </row>
     <row r="330">
@@ -19723,7 +19723,7 @@
         </is>
       </c>
       <c r="I330" t="n">
-        <v>203</v>
+        <v>203.68</v>
       </c>
       <c r="J330" s="1" t="n">
         <v>46101</v>
@@ -19741,7 +19741,7 @@
         <v>1001</v>
       </c>
       <c r="O330" t="n">
-        <v>2.671052631578947</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="331">
@@ -19778,7 +19778,7 @@
         </is>
       </c>
       <c r="I331" t="n">
-        <v>216</v>
+        <v>216.67</v>
       </c>
       <c r="J331" s="1" t="n">
         <v>46101</v>
@@ -19796,7 +19796,7 @@
         <v>1001</v>
       </c>
       <c r="O331" t="n">
-        <v>2.297872340425532</v>
+        <v>2.305</v>
       </c>
     </row>
     <row r="332">
@@ -19823,7 +19823,7 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>R$ 318.97</t>
+          <t>R$ 318,97</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
@@ -19837,7 +19837,7 @@
         </is>
       </c>
       <c r="I332" t="n">
-        <v>0</v>
+        <v>318.97</v>
       </c>
       <c r="J332" s="1" t="n">
         <v>46101</v>
@@ -19855,7 +19855,7 @@
         <v>1001</v>
       </c>
       <c r="O332" t="n">
-        <v>0</v>
+        <v>2.726239316239317</v>
       </c>
     </row>
     <row r="333">
@@ -19896,7 +19896,7 @@
         </is>
       </c>
       <c r="I333" t="n">
-        <v>295</v>
+        <v>295.12</v>
       </c>
       <c r="J333" s="1" t="n">
         <v>46101</v>
@@ -19914,7 +19914,7 @@
         <v>1001</v>
       </c>
       <c r="O333" t="n">
-        <v>3.241758241758242</v>
+        <v>3.243076923076923</v>
       </c>
     </row>
     <row r="334">
@@ -19955,7 +19955,7 @@
         </is>
       </c>
       <c r="I334" t="n">
-        <v>889</v>
+        <v>889.3</v>
       </c>
       <c r="J334" s="1" t="n">
         <v>46101</v>
@@ -19973,7 +19973,7 @@
         <v>1002</v>
       </c>
       <c r="O334" t="n">
-        <v>25.4</v>
+        <v>25.40857142857143</v>
       </c>
     </row>
     <row r="335">
@@ -20014,7 +20014,7 @@
         </is>
       </c>
       <c r="I335" t="n">
-        <v>1267</v>
+        <v>1267.93</v>
       </c>
       <c r="J335" s="1" t="n">
         <v>46101</v>
@@ -20032,7 +20032,7 @@
         <v>1002</v>
       </c>
       <c r="O335" t="n">
-        <v>27.54347826086957</v>
+        <v>27.56369565217392</v>
       </c>
     </row>
     <row r="336">
@@ -20073,7 +20073,7 @@
         </is>
       </c>
       <c r="I336" t="n">
-        <v>1747</v>
+        <v>1747.78</v>
       </c>
       <c r="J336" s="1" t="n">
         <v>46101</v>
@@ -20091,7 +20091,7 @@
         <v>1002</v>
       </c>
       <c r="O336" t="n">
-        <v>39.70454545454545</v>
+        <v>39.72227272727272</v>
       </c>
     </row>
     <row r="337">
@@ -20132,7 +20132,7 @@
         </is>
       </c>
       <c r="I337" t="n">
-        <v>963</v>
+        <v>963.29</v>
       </c>
       <c r="J337" s="1" t="n">
         <v>46101</v>
@@ -20150,7 +20150,7 @@
         <v>1002</v>
       </c>
       <c r="O337" t="n">
-        <v>23.48780487804878</v>
+        <v>23.49487804878049</v>
       </c>
     </row>
     <row r="338">
@@ -20191,7 +20191,7 @@
         </is>
       </c>
       <c r="I338" t="n">
-        <v>239</v>
+        <v>239.64</v>
       </c>
       <c r="J338" s="1" t="n">
         <v>46103</v>
@@ -20209,7 +20209,7 @@
         <v>1001</v>
       </c>
       <c r="O338" t="n">
-        <v>2.811764705882353</v>
+        <v>2.819294117647059</v>
       </c>
     </row>
     <row r="339">
@@ -20250,7 +20250,7 @@
         </is>
       </c>
       <c r="I339" t="n">
-        <v>128</v>
+        <v>128.65</v>
       </c>
       <c r="J339" s="1" t="n">
         <v>46103</v>
@@ -20268,7 +20268,7 @@
         <v>1001</v>
       </c>
       <c r="O339" t="n">
-        <v>2.844444444444445</v>
+        <v>2.858888888888889</v>
       </c>
     </row>
     <row r="340">
@@ -20295,7 +20295,7 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>R$ 298.08</t>
+          <t>R$ 298,08</t>
         </is>
       </c>
       <c r="G340" t="inlineStr"/>
@@ -20305,7 +20305,7 @@
         </is>
       </c>
       <c r="I340" t="n">
-        <v>0</v>
+        <v>298.08</v>
       </c>
       <c r="J340" s="1" t="n">
         <v>46103</v>
@@ -20323,7 +20323,7 @@
         <v>1001</v>
       </c>
       <c r="O340" t="n">
-        <v>0</v>
+        <v>2.614736842105263</v>
       </c>
     </row>
     <row r="341">
@@ -20364,7 +20364,7 @@
         </is>
       </c>
       <c r="I341" t="n">
-        <v>240</v>
+        <v>240.59</v>
       </c>
       <c r="J341" s="1" t="n">
         <v>46103</v>
@@ -20382,7 +20382,7 @@
         <v>1001</v>
       </c>
       <c r="O341" t="n">
-        <v>2.033898305084746</v>
+        <v>2.038898305084746</v>
       </c>
     </row>
     <row r="342">
@@ -20409,7 +20409,7 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>R$ 288.48</t>
+          <t>R$ 288,48</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
@@ -20423,7 +20423,7 @@
         </is>
       </c>
       <c r="I342" t="n">
-        <v>0</v>
+        <v>288.48</v>
       </c>
       <c r="J342" s="1" t="n">
         <v>46103</v>
@@ -20441,7 +20441,7 @@
         <v>1001</v>
       </c>
       <c r="O342" t="n">
-        <v>0</v>
+        <v>3.135652173913044</v>
       </c>
     </row>
     <row r="343">
@@ -20482,7 +20482,7 @@
         </is>
       </c>
       <c r="I343" t="n">
-        <v>686</v>
+        <v>686.26</v>
       </c>
       <c r="J343" s="1" t="n">
         <v>46104</v>
@@ -20500,7 +20500,7 @@
         <v>1002</v>
       </c>
       <c r="O343" t="n">
-        <v>13.45098039215686</v>
+        <v>13.45607843137255</v>
       </c>
     </row>
     <row r="344">
@@ -20541,7 +20541,7 @@
         </is>
       </c>
       <c r="I344" t="n">
-        <v>997</v>
+        <v>997.64</v>
       </c>
       <c r="J344" s="1" t="n">
         <v>46104</v>
@@ -20559,7 +20559,7 @@
         <v>1002</v>
       </c>
       <c r="O344" t="n">
-        <v>16.89830508474576</v>
+        <v>16.90915254237288</v>
       </c>
     </row>
     <row r="345">
@@ -20600,7 +20600,7 @@
         </is>
       </c>
       <c r="I345" t="n">
-        <v>703</v>
+        <v>703.17</v>
       </c>
       <c r="J345" s="1" t="n">
         <v>46104</v>
@@ -20618,7 +20618,7 @@
         <v>1002</v>
       </c>
       <c r="O345" t="n">
-        <v>18.02564102564103</v>
+        <v>18.03</v>
       </c>
     </row>
     <row r="346">
@@ -20659,7 +20659,7 @@
         </is>
       </c>
       <c r="I346" t="n">
-        <v>734</v>
+        <v>734.92</v>
       </c>
       <c r="J346" s="1" t="n">
         <v>46104</v>
@@ -20677,7 +20677,7 @@
         <v>1002</v>
       </c>
       <c r="O346" t="n">
-        <v>31.91304347826087</v>
+        <v>31.95304347826087</v>
       </c>
     </row>
     <row r="347">
@@ -20718,7 +20718,7 @@
         </is>
       </c>
       <c r="I347" t="n">
-        <v>234</v>
+        <v>234.16</v>
       </c>
       <c r="J347" s="1" t="n">
         <v>46105</v>
@@ -20736,7 +20736,7 @@
         <v>1001</v>
       </c>
       <c r="O347" t="n">
-        <v>3.162162162162162</v>
+        <v>3.164324324324324</v>
       </c>
     </row>
     <row r="348">
@@ -20777,7 +20777,7 @@
         </is>
       </c>
       <c r="I348" t="n">
-        <v>160</v>
+        <v>160.54</v>
       </c>
       <c r="J348" s="1" t="n">
         <v>46105</v>
@@ -20795,7 +20795,7 @@
         <v>1001</v>
       </c>
       <c r="O348" t="n">
-        <v>2.162162162162162</v>
+        <v>2.169459459459459</v>
       </c>
     </row>
     <row r="349">
@@ -20836,7 +20836,7 @@
         </is>
       </c>
       <c r="I349" t="n">
-        <v>207</v>
+        <v>207.34</v>
       </c>
       <c r="J349" s="1" t="n">
         <v>46105</v>
@@ -20854,7 +20854,7 @@
         <v>1001</v>
       </c>
       <c r="O349" t="n">
-        <v>2.134020618556701</v>
+        <v>2.137525773195876</v>
       </c>
     </row>
     <row r="350">
@@ -20895,7 +20895,7 @@
         </is>
       </c>
       <c r="I350" t="n">
-        <v>223</v>
+        <v>223.78</v>
       </c>
       <c r="J350" s="1" t="n">
         <v>46105</v>
@@ -20913,7 +20913,7 @@
         <v>1001</v>
       </c>
       <c r="O350" t="n">
-        <v>2.896103896103896</v>
+        <v>2.906233766233766</v>
       </c>
     </row>
     <row r="351">
@@ -20940,7 +20940,7 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>R$ 284.01</t>
+          <t>R$ 284,01</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
@@ -20954,7 +20954,7 @@
         </is>
       </c>
       <c r="I351" t="n">
-        <v>0</v>
+        <v>284.01</v>
       </c>
       <c r="J351" s="1" t="n">
         <v>46105</v>
@@ -20972,7 +20972,7 @@
         <v>1001</v>
       </c>
       <c r="O351" t="n">
-        <v>0</v>
+        <v>3.381071428571429</v>
       </c>
     </row>
     <row r="352">
@@ -21013,7 +21013,7 @@
         </is>
       </c>
       <c r="I352" t="n">
-        <v>578</v>
+        <v>578.96</v>
       </c>
       <c r="J352" s="1" t="n">
         <v>46106</v>
@@ -21031,7 +21031,7 @@
         <v>1002</v>
       </c>
       <c r="O352" t="n">
-        <v>17.51515151515152</v>
+        <v>17.54424242424243</v>
       </c>
     </row>
     <row r="353">
@@ -21072,7 +21072,7 @@
         </is>
       </c>
       <c r="I353" t="n">
-        <v>1204</v>
+        <v>1204.79</v>
       </c>
       <c r="J353" s="1" t="n">
         <v>46106</v>
@@ -21090,7 +21090,7 @@
         <v>1002</v>
       </c>
       <c r="O353" t="n">
-        <v>26.75555555555556</v>
+        <v>26.77311111111111</v>
       </c>
     </row>
     <row r="354">
@@ -21131,7 +21131,7 @@
         </is>
       </c>
       <c r="I354" t="n">
-        <v>767</v>
+        <v>767.0599999999999</v>
       </c>
       <c r="J354" s="1" t="n">
         <v>46106</v>
@@ -21149,7 +21149,7 @@
         <v>1002</v>
       </c>
       <c r="O354" t="n">
-        <v>25.56666666666667</v>
+        <v>25.56866666666667</v>
       </c>
     </row>
     <row r="355">
@@ -21190,7 +21190,7 @@
         </is>
       </c>
       <c r="I355" t="n">
-        <v>958</v>
+        <v>958.8</v>
       </c>
       <c r="J355" s="1" t="n">
         <v>46106</v>
@@ -21208,7 +21208,7 @@
         <v>1002</v>
       </c>
       <c r="O355" t="n">
-        <v>18.07547169811321</v>
+        <v>18.09056603773585</v>
       </c>
     </row>
     <row r="356">
@@ -21235,7 +21235,7 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>R$ 239.25</t>
+          <t>R$ 239,25</t>
         </is>
       </c>
       <c r="G356" t="inlineStr"/>
@@ -21245,7 +21245,7 @@
         </is>
       </c>
       <c r="I356" t="n">
-        <v>0</v>
+        <v>239.25</v>
       </c>
       <c r="J356" s="1" t="n">
         <v>46107</v>
@@ -21263,7 +21263,7 @@
         <v>1001</v>
       </c>
       <c r="O356" t="n">
-        <v>0</v>
+        <v>2.136160714285714</v>
       </c>
     </row>
     <row r="357">
@@ -21290,7 +21290,7 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>R$ 143.42</t>
+          <t>R$ 143,42</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
@@ -21304,7 +21304,7 @@
         </is>
       </c>
       <c r="I357" t="n">
-        <v>0</v>
+        <v>143.42</v>
       </c>
       <c r="J357" s="1" t="n">
         <v>46107</v>
@@ -21322,7 +21322,7 @@
         <v>1001</v>
       </c>
       <c r="O357" t="n">
-        <v>0</v>
+        <v>2.561071428571428</v>
       </c>
     </row>
     <row r="358">
@@ -21363,7 +21363,7 @@
         </is>
       </c>
       <c r="I358" t="n">
-        <v>191</v>
+        <v>191.1</v>
       </c>
       <c r="J358" s="1" t="n">
         <v>46107</v>
@@ -21381,7 +21381,7 @@
         <v>1001</v>
       </c>
       <c r="O358" t="n">
-        <v>2.48051948051948</v>
+        <v>2.481818181818182</v>
       </c>
     </row>
     <row r="359">
@@ -21422,7 +21422,7 @@
         </is>
       </c>
       <c r="I359" t="n">
-        <v>127</v>
+        <v>127.14</v>
       </c>
       <c r="J359" s="1" t="n">
         <v>46107</v>
@@ -21440,7 +21440,7 @@
         <v>1001</v>
       </c>
       <c r="O359" t="n">
-        <v>2.442307692307693</v>
+        <v>2.445</v>
       </c>
     </row>
     <row r="360">
@@ -21467,7 +21467,7 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>R$ 188.54</t>
+          <t>R$ 188,54</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
@@ -21481,7 +21481,7 @@
         </is>
       </c>
       <c r="I360" t="n">
-        <v>0</v>
+        <v>188.54</v>
       </c>
       <c r="J360" s="1" t="n">
         <v>46107</v>
@@ -21499,7 +21499,7 @@
         <v>1001</v>
       </c>
       <c r="O360" t="n">
-        <v>0</v>
+        <v>2.005744680851064</v>
       </c>
     </row>
     <row r="361">
@@ -21540,7 +21540,7 @@
         </is>
       </c>
       <c r="I361" t="n">
-        <v>2281</v>
+        <v>2281.39</v>
       </c>
       <c r="J361" s="1" t="n">
         <v>46108</v>
@@ -21558,7 +21558,7 @@
         <v>1002</v>
       </c>
       <c r="O361" t="n">
-        <v>38.66101694915254</v>
+        <v>38.66762711864406</v>
       </c>
     </row>
     <row r="362">
@@ -21599,7 +21599,7 @@
         </is>
       </c>
       <c r="I362" t="n">
-        <v>777</v>
+        <v>777.9</v>
       </c>
       <c r="J362" s="1" t="n">
         <v>46108</v>
@@ -21617,7 +21617,7 @@
         <v>1002</v>
       </c>
       <c r="O362" t="n">
-        <v>35.31818181818182</v>
+        <v>35.35909090909091</v>
       </c>
     </row>
     <row r="363">
@@ -21658,7 +21658,7 @@
         </is>
       </c>
       <c r="I363" t="n">
-        <v>1532</v>
+        <v>1532.92</v>
       </c>
       <c r="J363" s="1" t="n">
         <v>46108</v>
@@ -21676,7 +21676,7 @@
         <v>1002</v>
       </c>
       <c r="O363" t="n">
-        <v>35.62790697674419</v>
+        <v>35.6493023255814</v>
       </c>
     </row>
     <row r="364">
@@ -21717,7 +21717,7 @@
         </is>
       </c>
       <c r="I364" t="n">
-        <v>1351</v>
+        <v>1351.46</v>
       </c>
       <c r="J364" s="1" t="n">
         <v>46108</v>
@@ -21735,7 +21735,7 @@
         <v>1002</v>
       </c>
       <c r="O364" t="n">
-        <v>32.95121951219512</v>
+        <v>32.96243902439024</v>
       </c>
     </row>
     <row r="365">
@@ -21776,7 +21776,7 @@
         </is>
       </c>
       <c r="I365" t="n">
-        <v>243</v>
+        <v>243.55</v>
       </c>
       <c r="J365" s="1" t="n">
         <v>46109</v>
@@ -21794,7 +21794,7 @@
         <v>1001</v>
       </c>
       <c r="O365" t="n">
-        <v>2.479591836734694</v>
+        <v>2.485204081632653</v>
       </c>
     </row>
     <row r="366">
@@ -21835,7 +21835,7 @@
         </is>
       </c>
       <c r="I366" t="n">
-        <v>172</v>
+        <v>172.77</v>
       </c>
       <c r="J366" s="1" t="n">
         <v>46109</v>
@@ -21853,7 +21853,7 @@
         <v>1001</v>
       </c>
       <c r="O366" t="n">
-        <v>3.185185185185185</v>
+        <v>3.199444444444445</v>
       </c>
     </row>
     <row r="367">
@@ -21894,7 +21894,7 @@
         </is>
       </c>
       <c r="I367" t="n">
-        <v>143</v>
+        <v>143.8</v>
       </c>
       <c r="J367" s="1" t="n">
         <v>46109</v>
@@ -21912,7 +21912,7 @@
         <v>1001</v>
       </c>
       <c r="O367" t="n">
-        <v>3.325581395348837</v>
+        <v>3.344186046511628</v>
       </c>
     </row>
     <row r="368">
@@ -21953,7 +21953,7 @@
         </is>
       </c>
       <c r="I368" t="n">
-        <v>357</v>
+        <v>357.28</v>
       </c>
       <c r="J368" s="1" t="n">
         <v>46109</v>
@@ -21971,7 +21971,7 @@
         <v>1001</v>
       </c>
       <c r="O368" t="n">
-        <v>3.051282051282051</v>
+        <v>3.053675213675214</v>
       </c>
     </row>
     <row r="369">
@@ -22012,7 +22012,7 @@
         </is>
       </c>
       <c r="I369" t="n">
-        <v>168</v>
+        <v>168.5</v>
       </c>
       <c r="J369" s="1" t="n">
         <v>46109</v>
@@ -22030,7 +22030,7 @@
         <v>1001</v>
       </c>
       <c r="O369" t="n">
-        <v>3.428571428571428</v>
+        <v>3.438775510204082</v>
       </c>
     </row>
     <row r="370">
@@ -22071,7 +22071,7 @@
         </is>
       </c>
       <c r="I370" t="n">
-        <v>157</v>
+        <v>157.16</v>
       </c>
       <c r="J370" s="1" t="n">
         <v>46111</v>
@@ -22089,7 +22089,7 @@
         <v>1001</v>
       </c>
       <c r="O370" t="n">
-        <v>2.150684931506849</v>
+        <v>2.152876712328767</v>
       </c>
     </row>
     <row r="371">
@@ -22130,7 +22130,7 @@
         </is>
       </c>
       <c r="I371" t="n">
-        <v>222</v>
+        <v>222.66</v>
       </c>
       <c r="J371" s="1" t="n">
         <v>46111</v>
@@ -22148,7 +22148,7 @@
         <v>1001</v>
       </c>
       <c r="O371" t="n">
-        <v>3.126760563380282</v>
+        <v>3.136056338028169</v>
       </c>
     </row>
     <row r="372">
@@ -22189,7 +22189,7 @@
         </is>
       </c>
       <c r="I372" t="n">
-        <v>252</v>
+        <v>252.59</v>
       </c>
       <c r="J372" s="1" t="n">
         <v>46111</v>
@@ -22207,7 +22207,7 @@
         <v>1001</v>
       </c>
       <c r="O372" t="n">
-        <v>3.272727272727273</v>
+        <v>3.28038961038961</v>
       </c>
     </row>
     <row r="373">
@@ -22234,7 +22234,7 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>R$ 155.44</t>
+          <t>R$ 155,44</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
@@ -22248,7 +22248,7 @@
         </is>
       </c>
       <c r="I373" t="n">
-        <v>0</v>
+        <v>155.44</v>
       </c>
       <c r="J373" s="1" t="n">
         <v>46111</v>
@@ -22266,7 +22266,7 @@
         <v>1001</v>
       </c>
       <c r="O373" t="n">
-        <v>0</v>
+        <v>3.238333333333333</v>
       </c>
     </row>
     <row r="374">
@@ -22293,7 +22293,7 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>R$ 372.64</t>
+          <t>R$ 372,64</t>
         </is>
       </c>
       <c r="G374" t="inlineStr"/>
@@ -22303,7 +22303,7 @@
         </is>
       </c>
       <c r="I374" t="n">
-        <v>0</v>
+        <v>372.64</v>
       </c>
       <c r="J374" s="1" t="n">
         <v>46111</v>
@@ -22321,7 +22321,7 @@
         <v>1001</v>
       </c>
       <c r="O374" t="n">
-        <v>0</v>
+        <v>3.184957264957265</v>
       </c>
     </row>
     <row r="375">
@@ -22362,7 +22362,7 @@
         </is>
       </c>
       <c r="I375" t="n">
-        <v>639</v>
+        <v>639.8200000000001</v>
       </c>
       <c r="J375" s="1" t="n">
         <v>46111</v>
@@ -22380,7 +22380,7 @@
         <v>1002</v>
       </c>
       <c r="O375" t="n">
-        <v>18.79411764705882</v>
+        <v>18.81823529411765</v>
       </c>
     </row>
     <row r="376">
@@ -22421,7 +22421,7 @@
         </is>
       </c>
       <c r="I376" t="n">
-        <v>1210</v>
+        <v>1210.14</v>
       </c>
       <c r="J376" s="1" t="n">
         <v>46111</v>
@@ -22439,7 +22439,7 @@
         <v>1002</v>
       </c>
       <c r="O376" t="n">
-        <v>21.60714285714286</v>
+        <v>21.60964285714286</v>
       </c>
     </row>
     <row r="377">
@@ -22480,7 +22480,7 @@
         </is>
       </c>
       <c r="I377" t="n">
-        <v>1156</v>
+        <v>1156.18</v>
       </c>
       <c r="J377" s="1" t="n">
         <v>46111</v>
@@ -22498,7 +22498,7 @@
         <v>1002</v>
       </c>
       <c r="O377" t="n">
-        <v>21.81132075471698</v>
+        <v>21.81471698113208</v>
       </c>
     </row>
     <row r="378">
@@ -22539,7 +22539,7 @@
         </is>
       </c>
       <c r="I378" t="n">
-        <v>942</v>
+        <v>942.04</v>
       </c>
       <c r="J378" s="1" t="n">
         <v>46111</v>
@@ -22557,7 +22557,7 @@
         <v>1002</v>
       </c>
       <c r="O378" t="n">
-        <v>25.45945945945946</v>
+        <v>25.46054054054054</v>
       </c>
     </row>
     <row r="379">
@@ -22584,7 +22584,7 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>R$ 189.38</t>
+          <t>R$ 189,38</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
@@ -22598,7 +22598,7 @@
         </is>
       </c>
       <c r="I379" t="n">
-        <v>0</v>
+        <v>189.38</v>
       </c>
       <c r="J379" s="1" t="n">
         <v>46047</v>
@@ -22616,7 +22616,7 @@
         <v>1001</v>
       </c>
       <c r="O379" t="n">
-        <v>0</v>
+        <v>2.309512195121951</v>
       </c>
     </row>
     <row r="380">
@@ -22657,7 +22657,7 @@
         </is>
       </c>
       <c r="I380" t="n">
-        <v>128</v>
+        <v>128.59</v>
       </c>
       <c r="J380" s="1" t="n">
         <v>46079</v>
@@ -22675,7 +22675,7 @@
         <v>1001</v>
       </c>
       <c r="O380" t="n">
-        <v>2.169491525423729</v>
+        <v>2.179491525423729</v>
       </c>
     </row>
     <row r="381">
@@ -22716,7 +22716,7 @@
         </is>
       </c>
       <c r="I381" t="n">
-        <v>644</v>
+        <v>644.29</v>
       </c>
       <c r="J381" s="1" t="n">
         <v>46073</v>
@@ -22734,7 +22734,7 @@
         <v>1002</v>
       </c>
       <c r="O381" t="n">
-        <v>29.27272727272727</v>
+        <v>29.28590909090909</v>
       </c>
     </row>
     <row r="382">
@@ -22775,7 +22775,7 @@
         </is>
       </c>
       <c r="I382" t="n">
-        <v>203</v>
+        <v>203.09</v>
       </c>
       <c r="J382" s="1" t="n">
         <v>46055</v>
@@ -22793,7 +22793,7 @@
         <v>1001</v>
       </c>
       <c r="O382" t="n">
-        <v>2.071428571428572</v>
+        <v>2.07234693877551</v>
       </c>
     </row>
     <row r="383">
@@ -22834,7 +22834,7 @@
         </is>
       </c>
       <c r="I383" t="n">
-        <v>295</v>
+        <v>295.12</v>
       </c>
       <c r="J383" s="1" t="n">
         <v>46101</v>
@@ -22852,7 +22852,7 @@
         <v>1001</v>
       </c>
       <c r="O383" t="n">
-        <v>3.241758241758242</v>
+        <v>3.243076923076923</v>
       </c>
     </row>
     <row r="384">
@@ -22893,7 +22893,7 @@
         </is>
       </c>
       <c r="I384" t="n">
-        <v>753</v>
+        <v>753.7</v>
       </c>
       <c r="J384" s="1" t="n">
         <v>46024</v>
@@ -22911,7 +22911,7 @@
         <v>1002</v>
       </c>
       <c r="O384" t="n">
-        <v>35.85714285714285</v>
+        <v>35.89047619047619</v>
       </c>
     </row>
     <row r="385">
@@ -22938,7 +22938,7 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>R$ 97.72</t>
+          <t>R$ 97,72</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
@@ -22952,7 +22952,7 @@
         </is>
       </c>
       <c r="I385" t="n">
-        <v>0</v>
+        <v>97.72</v>
       </c>
       <c r="J385" s="1" t="n">
         <v>46097</v>
@@ -22970,7 +22970,7 @@
         <v>1001</v>
       </c>
       <c r="O385" t="n">
-        <v>0</v>
+        <v>2.326666666666667</v>
       </c>
     </row>
     <row r="386">
@@ -22997,7 +22997,7 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>R$ 235.77</t>
+          <t>R$ 235,77</t>
         </is>
       </c>
       <c r="G386" t="inlineStr"/>
@@ -23007,7 +23007,7 @@
         </is>
       </c>
       <c r="I386" t="n">
-        <v>0</v>
+        <v>235.77</v>
       </c>
       <c r="J386" s="1" t="n">
         <v>46047</v>
@@ -23025,7 +23025,7 @@
         <v>1001</v>
       </c>
       <c r="O386" t="n">
-        <v>0</v>
+        <v>3.186081081081081</v>
       </c>
     </row>
     <row r="387">
@@ -23066,7 +23066,7 @@
         </is>
       </c>
       <c r="I387" t="n">
-        <v>1412</v>
+        <v>1412.64</v>
       </c>
       <c r="J387" s="1" t="n">
         <v>46064</v>
@@ -23084,7 +23084,7 @@
         <v>1002</v>
       </c>
       <c r="O387" t="n">
-        <v>29.41666666666667</v>
+        <v>29.43</v>
       </c>
     </row>
     <row r="388">
@@ -23111,7 +23111,7 @@
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>R$ 332.22</t>
+          <t>R$ 332,22</t>
         </is>
       </c>
       <c r="G388" t="inlineStr"/>
@@ -23121,7 +23121,7 @@
         </is>
       </c>
       <c r="I388" t="n">
-        <v>0</v>
+        <v>332.22</v>
       </c>
       <c r="J388" s="1" t="n">
         <v>46063</v>
@@ -23139,7 +23139,7 @@
         <v>1001</v>
       </c>
       <c r="O388" t="n">
-        <v>0</v>
+        <v>2.7685</v>
       </c>
     </row>
     <row r="389">
@@ -23180,7 +23180,7 @@
         </is>
       </c>
       <c r="I389" t="n">
-        <v>280</v>
+        <v>280.25</v>
       </c>
       <c r="J389" s="1" t="n">
         <v>46045</v>
@@ -23198,7 +23198,7 @@
         <v>1002</v>
       </c>
       <c r="O389" t="n">
-        <v>14</v>
+        <v>14.0125</v>
       </c>
     </row>
     <row r="390">
@@ -23225,7 +23225,7 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>R$ 351.95</t>
+          <t>R$ 351,95</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
@@ -23239,7 +23239,7 @@
         </is>
       </c>
       <c r="I390" t="n">
-        <v>0</v>
+        <v>351.95</v>
       </c>
       <c r="J390" s="1" t="n">
         <v>46091</v>
@@ -23257,7 +23257,7 @@
         <v>1001</v>
       </c>
       <c r="O390" t="n">
-        <v>0</v>
+        <v>3.087280701754386</v>
       </c>
     </row>
     <row r="391">
@@ -23298,7 +23298,7 @@
         </is>
       </c>
       <c r="I391" t="n">
-        <v>145</v>
+        <v>145.59</v>
       </c>
       <c r="J391" s="1" t="n">
         <v>46043</v>
@@ -23316,7 +23316,7 @@
         <v>1001</v>
       </c>
       <c r="O391" t="n">
-        <v>2.959183673469388</v>
+        <v>2.971224489795918</v>
       </c>
     </row>
     <row r="392">
@@ -23357,7 +23357,7 @@
         </is>
       </c>
       <c r="I392" t="n">
-        <v>128</v>
+        <v>128.65</v>
       </c>
       <c r="J392" s="1" t="n">
         <v>46103</v>
@@ -23375,7 +23375,7 @@
         <v>1001</v>
       </c>
       <c r="O392" t="n">
-        <v>2.844444444444445</v>
+        <v>2.858888888888889</v>
       </c>
     </row>
     <row r="393">
@@ -23416,7 +23416,7 @@
         </is>
       </c>
       <c r="I393" t="n">
-        <v>585</v>
+        <v>585.8200000000001</v>
       </c>
       <c r="J393" s="1" t="n">
         <v>46052</v>
@@ -23434,7 +23434,7 @@
         <v>1002</v>
       </c>
       <c r="O393" t="n">
-        <v>22.5</v>
+        <v>22.53153846153846</v>
       </c>
     </row>
     <row r="394">
@@ -23475,7 +23475,7 @@
         </is>
       </c>
       <c r="I394" t="n">
-        <v>335</v>
+        <v>335.78</v>
       </c>
       <c r="J394" s="1" t="n">
         <v>46023</v>
@@ -23493,7 +23493,7 @@
         <v>1001</v>
       </c>
       <c r="O394" t="n">
-        <v>2.815126050420168</v>
+        <v>2.821680672268907</v>
       </c>
     </row>
     <row r="395">
@@ -23534,7 +23534,7 @@
         </is>
       </c>
       <c r="I395" t="n">
-        <v>816</v>
+        <v>816.53</v>
       </c>
       <c r="J395" s="1" t="n">
         <v>46078</v>
@@ -23552,7 +23552,7 @@
         <v>1002</v>
       </c>
       <c r="O395" t="n">
-        <v>19.90243902439024</v>
+        <v>19.91536585365854</v>
       </c>
     </row>
     <row r="396">
@@ -23593,7 +23593,7 @@
         </is>
       </c>
       <c r="I396" t="n">
-        <v>222</v>
+        <v>222.66</v>
       </c>
       <c r="J396" s="1" t="n">
         <v>46111</v>
@@ -23611,7 +23611,7 @@
         <v>1001</v>
       </c>
       <c r="O396" t="n">
-        <v>3.126760563380282</v>
+        <v>3.136056338028169</v>
       </c>
     </row>
     <row r="397">
@@ -23638,7 +23638,7 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>R$ 122.79</t>
+          <t>R$ 122,79</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
@@ -23652,7 +23652,7 @@
         </is>
       </c>
       <c r="I397" t="n">
-        <v>0</v>
+        <v>122.79</v>
       </c>
       <c r="J397" s="1" t="n">
         <v>46077</v>
@@ -23670,7 +23670,7 @@
         <v>1001</v>
       </c>
       <c r="O397" t="n">
-        <v>0</v>
+        <v>2.0465</v>
       </c>
     </row>
     <row r="398">
@@ -23711,7 +23711,7 @@
         </is>
       </c>
       <c r="I398" t="n">
-        <v>157</v>
+        <v>157.41</v>
       </c>
       <c r="J398" s="1" t="n">
         <v>46101</v>
@@ -23729,7 +23729,7 @@
         <v>1001</v>
       </c>
       <c r="O398" t="n">
-        <v>3.07843137254902</v>
+        <v>3.086470588235294</v>
       </c>
     </row>
     <row r="399">
@@ -23770,7 +23770,7 @@
         </is>
       </c>
       <c r="I399" t="n">
-        <v>239</v>
+        <v>239.64</v>
       </c>
       <c r="J399" s="1" t="n">
         <v>46103</v>
@@ -23788,7 +23788,7 @@
         <v>1001</v>
       </c>
       <c r="O399" t="n">
-        <v>2.811764705882353</v>
+        <v>2.819294117647059</v>
       </c>
     </row>
     <row r="400">
@@ -23829,7 +23829,7 @@
         </is>
       </c>
       <c r="I400" t="n">
-        <v>566</v>
+        <v>566.55</v>
       </c>
       <c r="J400" s="1" t="n">
         <v>46043</v>
@@ -23847,7 +23847,7 @@
         <v>1002</v>
       </c>
       <c r="O400" t="n">
-        <v>17.15151515151515</v>
+        <v>17.16818181818182</v>
       </c>
     </row>
     <row r="401">
@@ -23888,7 +23888,7 @@
         </is>
       </c>
       <c r="I401" t="n">
-        <v>197</v>
+        <v>197.98</v>
       </c>
       <c r="J401" s="1" t="n">
         <v>46099</v>
@@ -23906,7 +23906,7 @@
         <v>1001</v>
       </c>
       <c r="O401" t="n">
-        <v>2.940298507462686</v>
+        <v>2.954925373134328</v>
       </c>
     </row>
     <row r="402">
@@ -23947,7 +23947,7 @@
         </is>
       </c>
       <c r="I402" t="n">
-        <v>240</v>
+        <v>240.59</v>
       </c>
       <c r="J402" s="1" t="n">
         <v>46103</v>
@@ -23965,7 +23965,7 @@
         <v>1001</v>
       </c>
       <c r="O402" t="n">
-        <v>2.033898305084746</v>
+        <v>2.038898305084746</v>
       </c>
     </row>
     <row r="403">
@@ -24006,7 +24006,7 @@
         </is>
       </c>
       <c r="I403" t="n">
-        <v>1536</v>
+        <v>1536.61</v>
       </c>
       <c r="J403" s="1" t="n">
         <v>46094</v>
@@ -24024,7 +24024,7 @@
         <v>1002</v>
       </c>
       <c r="O403" t="n">
-        <v>32.68085106382978</v>
+        <v>32.69382978723404</v>
       </c>
     </row>
   </sheetData>
